--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC95C6E4-4FD8-4090-A7F1-DBFAA8739047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7876A73D-AA23-495B-950A-F50662BEF8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -192,6 +192,21 @@
   </si>
   <si>
     <t>ENJOYED FRESHER'S PARTY</t>
+  </si>
+  <si>
+    <t>NORMAL DAY</t>
+  </si>
+  <si>
+    <t>VERY UNSATISFIED</t>
+  </si>
+  <si>
+    <t>RELAXED AT WEEKEND</t>
+  </si>
+  <si>
+    <t>TAUGHT MY COUSIN</t>
+  </si>
+  <si>
+    <t>STUDIED PYTHON FOR CA</t>
   </si>
 </sst>
 </file>
@@ -780,7 +795,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I28" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I32" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -876,7 +891,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J28" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J32" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -1816,73 +1831,185 @@
       <c r="A29" s="10">
         <v>46276</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="14"/>
+      <c r="B29" s="11">
+        <v>320</v>
+      </c>
+      <c r="C29" s="11">
+        <v>50</v>
+      </c>
+      <c r="D29" s="11">
+        <v>135</v>
+      </c>
+      <c r="E29" s="11">
+        <v>80</v>
+      </c>
+      <c r="F29" s="11">
+        <v>360</v>
+      </c>
+      <c r="G29" s="11">
+        <v>6</v>
+      </c>
+      <c r="H29" s="11">
+        <v>165</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J29" s="6">
+        <f t="shared" si="1"/>
+        <v>330</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>46277</v>
       </c>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="14"/>
+      <c r="B30" s="11">
+        <v>350</v>
+      </c>
+      <c r="C30" s="11">
+        <v>75</v>
+      </c>
+      <c r="D30" s="11">
+        <v>115</v>
+      </c>
+      <c r="E30" s="11">
+        <v>90</v>
+      </c>
+      <c r="F30" s="11">
+        <v>0</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11">
+        <v>195</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="0"/>
+        <v>825</v>
+      </c>
+      <c r="J30" s="6">
+        <f t="shared" si="1"/>
+        <v>615</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>46278</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="14"/>
+      <c r="B31" s="11">
+        <v>300</v>
+      </c>
+      <c r="C31" s="11">
+        <v>80</v>
+      </c>
+      <c r="D31" s="11">
+        <v>105</v>
+      </c>
+      <c r="E31" s="11">
+        <v>85</v>
+      </c>
+      <c r="F31" s="11">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>210</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J31" s="6">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>46279</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="14"/>
+      <c r="B32" s="11">
+        <v>400</v>
+      </c>
+      <c r="C32" s="11">
+        <v>65</v>
+      </c>
+      <c r="D32" s="11">
+        <v>120</v>
+      </c>
+      <c r="E32" s="11">
+        <v>100</v>
+      </c>
+      <c r="F32" s="11">
+        <v>220</v>
+      </c>
+      <c r="G32" s="11">
+        <v>4</v>
+      </c>
+      <c r="H32" s="11">
+        <v>180</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="0"/>
+        <v>1085</v>
+      </c>
+      <c r="J32" s="6">
+        <f t="shared" si="1"/>
+        <v>355</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7876A73D-AA23-495B-950A-F50662BEF8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFAAF6B-BFF9-4451-9D73-595DAB04E5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="58">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>STUDIED PYTHON FOR CA</t>
+  </si>
+  <si>
+    <t>FOCUS ON VARIOUS TASKS</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I32" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I33" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -891,7 +894,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J32" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J33" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -2015,19 +2018,47 @@
       <c r="A33" s="10">
         <v>46280</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="14"/>
+      <c r="B33" s="11">
+        <v>360</v>
+      </c>
+      <c r="C33" s="11">
+        <v>60</v>
+      </c>
+      <c r="D33" s="11">
+        <v>125</v>
+      </c>
+      <c r="E33" s="11">
+        <v>95</v>
+      </c>
+      <c r="F33" s="11">
+        <v>300</v>
+      </c>
+      <c r="G33" s="11">
+        <v>5</v>
+      </c>
+      <c r="H33" s="11">
+        <v>175</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="0"/>
+        <v>1115</v>
+      </c>
+      <c r="J33" s="6">
+        <f t="shared" si="1"/>
+        <v>325</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFAAF6B-BFF9-4451-9D73-595DAB04E5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A14DE-F12B-4A71-9617-C2A782FCE416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>FOCUS ON VARIOUS TASKS</t>
+  </si>
+  <si>
+    <t>BLISSFUL DAY</t>
   </si>
 </sst>
 </file>
@@ -798,7 +801,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" ref="I6:I33" si="0">SUM(B6:F6,H6)</f>
+        <f t="shared" ref="I6:I34" si="0">SUM(B6:F6,H6)</f>
         <v>1090</v>
       </c>
       <c r="J6" s="5">
@@ -894,7 +897,7 @@
         <v>1115</v>
       </c>
       <c r="J8" s="5">
-        <f t="shared" ref="J8:J33" si="1">1440-I8</f>
+        <f t="shared" ref="J8:J34" si="1">1440-I8</f>
         <v>325</v>
       </c>
       <c r="K8" s="11" t="s">
@@ -2064,19 +2067,47 @@
       <c r="A34" s="10">
         <v>46281</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="14"/>
+      <c r="B34" s="11">
+        <v>390</v>
+      </c>
+      <c r="C34" s="11">
+        <v>70</v>
+      </c>
+      <c r="D34" s="11">
+        <v>130</v>
+      </c>
+      <c r="E34" s="11">
+        <v>90</v>
+      </c>
+      <c r="F34" s="11">
+        <v>350</v>
+      </c>
+      <c r="G34" s="11">
+        <v>5</v>
+      </c>
+      <c r="H34" s="11">
+        <v>190</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="0"/>
+        <v>1220</v>
+      </c>
+      <c r="J34" s="6">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623A14DE-F12B-4A71-9617-C2A782FCE416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3728CF-DD34-442E-8B74-44F576491268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="65">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -213,6 +213,24 @@
   </si>
   <si>
     <t>BLISSFUL DAY</t>
+  </si>
+  <si>
+    <t>BALANCED ROUTINE</t>
+  </si>
+  <si>
+    <t>RECOVERY SUNDAY</t>
+  </si>
+  <si>
+    <t>STEADY STUDYING</t>
+  </si>
+  <si>
+    <t>LIGHT LOAD DAY</t>
+  </si>
+  <si>
+    <t>EFFICIENT WORKFLOW</t>
+  </si>
+  <si>
+    <t>FOCUSED MINDSET</t>
   </si>
 </sst>
 </file>
@@ -278,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -321,6 +339,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
@@ -729,455 +753,455 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+    <row r="5" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
+        <v>46247</v>
+      </c>
+      <c r="B5" s="13">
+        <v>420</v>
+      </c>
+      <c r="C5" s="13">
+        <v>55</v>
+      </c>
+      <c r="D5" s="13">
+        <v>120</v>
+      </c>
+      <c r="E5" s="13">
+        <v>90</v>
+      </c>
+      <c r="F5" s="13">
+        <v>450</v>
+      </c>
+      <c r="G5" s="13">
+        <v>8</v>
+      </c>
+      <c r="H5" s="13">
+        <v>150</v>
+      </c>
+      <c r="I5" s="17">
+        <f>SUM(B5:F5,H5)</f>
+        <v>1285</v>
+      </c>
+      <c r="J5" s="17">
+        <f>1440-I5</f>
+        <v>155</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
+        <v>46248</v>
+      </c>
+      <c r="B6" s="13">
+        <v>360</v>
+      </c>
+      <c r="C6" s="13">
+        <v>45</v>
+      </c>
+      <c r="D6" s="13">
+        <v>160</v>
+      </c>
+      <c r="E6" s="13">
+        <v>60</v>
+      </c>
+      <c r="F6" s="13">
+        <v>350</v>
+      </c>
+      <c r="G6" s="13">
+        <v>7</v>
+      </c>
+      <c r="H6" s="13">
+        <v>120</v>
+      </c>
+      <c r="I6" s="17">
+        <f t="shared" ref="I6:I9" si="0">SUM(B6:F6,H6)</f>
+        <v>1095</v>
+      </c>
+      <c r="J6" s="17">
+        <f t="shared" ref="J6:J9" si="1">1440-I6</f>
+        <v>345</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16">
+        <v>46249</v>
+      </c>
+      <c r="B7" s="13">
+        <v>450</v>
+      </c>
+      <c r="C7" s="13">
+        <v>75</v>
+      </c>
+      <c r="D7" s="13">
+        <v>90</v>
+      </c>
+      <c r="E7" s="13">
+        <v>100</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>200</v>
+      </c>
+      <c r="I7" s="17">
+        <f t="shared" si="0"/>
+        <v>915</v>
+      </c>
+      <c r="J7" s="17">
+        <f t="shared" si="1"/>
+        <v>525</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16">
+        <v>46250</v>
+      </c>
+      <c r="B8" s="13">
+        <v>480</v>
+      </c>
+      <c r="C8" s="13">
+        <v>60</v>
+      </c>
+      <c r="D8" s="13">
+        <v>110</v>
+      </c>
+      <c r="E8" s="13">
+        <v>80</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>180</v>
+      </c>
+      <c r="I8" s="17">
+        <f t="shared" si="0"/>
+        <v>910</v>
+      </c>
+      <c r="J8" s="17">
+        <f t="shared" si="1"/>
+        <v>530</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16">
+        <v>46251</v>
+      </c>
+      <c r="B9" s="13">
+        <v>390</v>
+      </c>
+      <c r="C9" s="13">
+        <v>65</v>
+      </c>
+      <c r="D9" s="13">
+        <v>105</v>
+      </c>
+      <c r="E9" s="13">
+        <v>85</v>
+      </c>
+      <c r="F9" s="13">
+        <v>200</v>
+      </c>
+      <c r="G9" s="13">
+        <v>4</v>
+      </c>
+      <c r="H9" s="13">
+        <v>110</v>
+      </c>
+      <c r="I9" s="17">
+        <f t="shared" si="0"/>
+        <v>955</v>
+      </c>
+      <c r="J9" s="17">
+        <f t="shared" si="1"/>
+        <v>485</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
         <v>46252</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B10" s="12">
         <v>420</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C10" s="12">
         <v>60</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D10" s="12">
         <v>90</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E10" s="12">
         <v>75</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F10" s="12">
         <v>300</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G10" s="12">
         <v>6</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H10" s="12">
         <v>90</v>
       </c>
-      <c r="I5" s="5">
-        <f>SUM(B5:F5,H5)</f>
+      <c r="I10" s="5">
+        <f>SUM(B10:F10,H10)</f>
         <v>1035</v>
       </c>
-      <c r="J5" s="5">
-        <f>1440-I5</f>
+      <c r="J10" s="5">
+        <f>1440-I10</f>
         <v>405</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K10" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L10" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N10" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+    <row r="11" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
         <v>46253</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B11" s="12">
         <v>360</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C11" s="12">
         <v>40</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D11" s="12">
         <v>80</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E11" s="12">
         <v>90</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F11" s="12">
         <v>400</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G11" s="12">
         <v>7</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H11" s="12">
         <v>120</v>
       </c>
-      <c r="I6" s="5">
-        <f t="shared" ref="I6:I34" si="0">SUM(B6:F6,H6)</f>
+      <c r="I11" s="5">
+        <f t="shared" ref="I11:I40" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
-      <c r="J6" s="5">
-        <f>1440-I6</f>
+      <c r="J11" s="5">
+        <f>1440-I11</f>
         <v>350</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N11" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
         <v>46254</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B12" s="11">
         <v>390</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C12" s="11">
         <v>55</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D12" s="11">
         <v>75</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E12" s="11">
         <v>60</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F12" s="11">
         <v>450</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G12" s="11">
         <v>8</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H12" s="11">
         <v>100</v>
       </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
+      <c r="I12" s="5">
+        <f t="shared" si="2"/>
         <v>1130</v>
       </c>
-      <c r="J7" s="5">
-        <f>1440-I7</f>
+      <c r="J12" s="5">
+        <f>1440-I12</f>
         <v>310</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
-        <v>46255</v>
-      </c>
-      <c r="B8" s="11">
-        <v>400</v>
-      </c>
-      <c r="C8" s="11">
-        <v>60</v>
-      </c>
-      <c r="D8" s="11">
-        <v>100</v>
-      </c>
-      <c r="E8" s="11">
-        <v>55</v>
-      </c>
-      <c r="F8" s="11">
-        <v>350</v>
-      </c>
-      <c r="G8" s="11">
-        <v>7</v>
-      </c>
-      <c r="H8" s="11">
-        <v>150</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>1115</v>
-      </c>
-      <c r="J8" s="5">
-        <f t="shared" ref="J8:J34" si="1">1440-I8</f>
-        <v>325</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
-        <v>46256</v>
-      </c>
-      <c r="B9" s="11">
-        <v>480</v>
-      </c>
-      <c r="C9" s="11">
-        <v>40</v>
-      </c>
-      <c r="D9" s="11">
-        <v>85</v>
-      </c>
-      <c r="E9" s="11">
-        <v>80</v>
-      </c>
-      <c r="F9" s="11">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <v>170</v>
-      </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>855</v>
-      </c>
-      <c r="J9" s="5">
-        <f t="shared" si="1"/>
-        <v>585</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
-        <v>46257</v>
-      </c>
-      <c r="B10" s="11">
-        <v>450</v>
-      </c>
-      <c r="C10" s="11">
-        <v>50</v>
-      </c>
-      <c r="D10" s="11">
-        <v>150</v>
-      </c>
-      <c r="E10" s="11">
-        <v>150</v>
-      </c>
-      <c r="F10" s="11">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
-        <v>250</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="J10" s="5">
-        <f t="shared" si="1"/>
-        <v>390</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
-        <v>46258</v>
-      </c>
-      <c r="B11" s="11">
-        <v>400</v>
-      </c>
-      <c r="C11" s="11">
-        <v>55</v>
-      </c>
-      <c r="D11" s="11">
-        <v>175</v>
-      </c>
-      <c r="E11" s="11">
-        <v>80</v>
-      </c>
-      <c r="F11" s="11">
-        <v>200</v>
-      </c>
-      <c r="G11" s="11">
-        <v>4</v>
-      </c>
-      <c r="H11" s="11">
-        <v>200</v>
-      </c>
-      <c r="I11" s="6">
-        <f t="shared" si="0"/>
-        <v>1110</v>
-      </c>
-      <c r="J11" s="6">
-        <f t="shared" si="1"/>
-        <v>330</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
-        <v>46259</v>
-      </c>
-      <c r="B12" s="11">
-        <v>320</v>
-      </c>
-      <c r="C12" s="11">
-        <v>80</v>
-      </c>
-      <c r="D12" s="11">
-        <v>90</v>
-      </c>
-      <c r="E12" s="11">
-        <v>120</v>
-      </c>
-      <c r="F12" s="11">
-        <v>300</v>
-      </c>
-      <c r="G12" s="11">
-        <v>5</v>
-      </c>
-      <c r="H12" s="11">
-        <v>190</v>
-      </c>
-      <c r="I12" s="6">
-        <f t="shared" si="0"/>
-        <v>1100</v>
-      </c>
-      <c r="J12" s="6">
-        <f t="shared" si="1"/>
-        <v>340</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>7</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
-        <v>46260</v>
+        <v>46255</v>
       </c>
       <c r="B13" s="11">
-        <v>470</v>
+        <v>400</v>
       </c>
       <c r="C13" s="11">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D13" s="11">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="E13" s="11">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F13" s="11">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G13" s="11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H13" s="11">
-        <v>200</v>
-      </c>
-      <c r="I13" s="6">
-        <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J13" s="6">
-        <f t="shared" si="1"/>
-        <v>470</v>
+        <v>150</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="2"/>
+        <v>1115</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" ref="J13:J40" si="3">1440-I13</f>
+        <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>28</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
-        <v>46261</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="11">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="C14" s="11">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E14" s="11">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F14" s="11">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G14" s="11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="11">
-        <v>160</v>
-      </c>
-      <c r="I14" s="6">
-        <f t="shared" si="0"/>
-        <v>1090</v>
-      </c>
-      <c r="J14" s="6">
-        <f t="shared" si="1"/>
-        <v>350</v>
+        <v>170</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="2"/>
+        <v>855</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="3"/>
+        <v>585</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>29</v>
@@ -1186,458 +1210,458 @@
         <v>27</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
-        <v>46262</v>
+        <v>46257</v>
       </c>
       <c r="B15" s="11">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="C15" s="11">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D15" s="11">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="E15" s="11">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="F15" s="11">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11">
-        <v>200</v>
-      </c>
-      <c r="I15" s="6">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J15" s="6">
-        <f t="shared" si="1"/>
-        <v>540</v>
+        <v>250</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="2"/>
+        <v>1050</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="3"/>
+        <v>390</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L15" s="11" t="s">
         <v>10</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
-        <v>46263</v>
+        <v>46258</v>
       </c>
       <c r="B16" s="11">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C16" s="11">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D16" s="11">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="E16" s="11">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F16" s="11">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G16" s="11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" s="11">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="0"/>
-        <v>815</v>
+        <f t="shared" si="2"/>
+        <v>1110</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="1"/>
-        <v>625</v>
+        <f t="shared" si="3"/>
+        <v>330</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
-        <v>46264</v>
+        <v>46259</v>
       </c>
       <c r="B17" s="11">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="C17" s="11">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D17" s="11">
+        <v>90</v>
+      </c>
+      <c r="E17" s="11">
         <v>120</v>
       </c>
-      <c r="E17" s="11">
-        <v>100</v>
-      </c>
       <c r="F17" s="11">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G17" s="11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="11">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="I17" s="6">
-        <f t="shared" si="0"/>
-        <v>875</v>
+        <f t="shared" si="2"/>
+        <v>1100</v>
       </c>
       <c r="J17" s="6">
-        <f t="shared" si="1"/>
-        <v>565</v>
+        <f t="shared" si="3"/>
+        <v>340</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>5</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B18" s="11">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="C18" s="11">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D18" s="11">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="E18" s="11">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F18" s="11">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0</v>
+      </c>
+      <c r="H18" s="11">
         <v>200</v>
       </c>
-      <c r="G18" s="11">
-        <v>4</v>
-      </c>
-      <c r="H18" s="11">
-        <v>190</v>
-      </c>
       <c r="I18" s="6">
-        <f t="shared" si="0"/>
-        <v>1080</v>
+        <f t="shared" si="2"/>
+        <v>970</v>
       </c>
       <c r="J18" s="6">
-        <f t="shared" si="1"/>
-        <v>360</v>
+        <f t="shared" si="3"/>
+        <v>470</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>9</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B19" s="11">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C19" s="11">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D19" s="11">
         <v>95</v>
       </c>
       <c r="E19" s="11">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F19" s="11">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G19" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" s="11">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" si="0"/>
-        <v>1030</v>
+        <f t="shared" si="2"/>
+        <v>1090</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="1"/>
-        <v>410</v>
+        <f t="shared" si="3"/>
+        <v>350</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="B20" s="11">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="C20" s="11">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D20" s="11">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="E20" s="11">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F20" s="11">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G20" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="11">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="I20" s="6">
-        <f t="shared" si="0"/>
-        <v>1125</v>
+        <f t="shared" si="2"/>
+        <v>900</v>
       </c>
       <c r="J20" s="6">
-        <f t="shared" si="1"/>
-        <v>315</v>
+        <f t="shared" si="3"/>
+        <v>540</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
-        <v>46268</v>
+        <v>46263</v>
       </c>
       <c r="B21" s="11">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="C21" s="11">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D21" s="11">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E21" s="11">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F21" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G21" s="11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" s="11">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="0"/>
-        <v>1030</v>
+        <f t="shared" si="2"/>
+        <v>815</v>
       </c>
       <c r="J21" s="6">
-        <f t="shared" si="1"/>
-        <v>410</v>
+        <f t="shared" si="3"/>
+        <v>625</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>7</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
-        <v>46269</v>
+        <v>46264</v>
       </c>
       <c r="B22" s="11">
-        <v>370</v>
+        <v>420</v>
       </c>
       <c r="C22" s="11">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D22" s="11">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="E22" s="11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F22" s="11">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G22" s="11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H22" s="11">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" si="0"/>
-        <v>1145</v>
+        <f t="shared" si="2"/>
+        <v>875</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="1"/>
-        <v>295</v>
+        <f t="shared" si="3"/>
+        <v>565</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
-        <v>46270</v>
+        <v>46265</v>
       </c>
       <c r="B23" s="11">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C23" s="11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D23" s="11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E23" s="11">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F23" s="11">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G23" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H23" s="11">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="0"/>
-        <v>955</v>
+        <f t="shared" si="2"/>
+        <v>1080</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="1"/>
-        <v>485</v>
+        <f t="shared" si="3"/>
+        <v>360</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
-        <v>46271</v>
+        <v>46266</v>
       </c>
       <c r="B24" s="11">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C24" s="11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D24" s="11">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="E24" s="11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F24" s="11">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G24" s="11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="11">
         <v>180</v>
       </c>
       <c r="I24" s="6">
-        <f t="shared" si="0"/>
-        <v>875</v>
+        <f t="shared" si="2"/>
+        <v>1030</v>
       </c>
       <c r="J24" s="6">
-        <f t="shared" si="1"/>
-        <v>565</v>
+        <f t="shared" si="3"/>
+        <v>410</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L24" s="11" t="s">
         <v>28</v>
@@ -1646,182 +1670,182 @@
         <v>11</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="B25" s="11">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="C25" s="11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D25" s="11">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E25" s="11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F25" s="11">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="G25" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="11">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="0"/>
-        <v>1160</v>
+        <f t="shared" si="2"/>
+        <v>1125</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="1"/>
-        <v>280</v>
+        <f t="shared" si="3"/>
+        <v>315</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
-        <v>46273</v>
+        <v>46268</v>
       </c>
       <c r="B26" s="11">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="C26" s="11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D26" s="11">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="E26" s="11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F26" s="11">
         <v>300</v>
       </c>
       <c r="G26" s="11">
+        <v>6</v>
+      </c>
+      <c r="H26" s="11">
+        <v>165</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+      <c r="J26" s="6">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+      <c r="K26" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="11">
-        <v>175</v>
-      </c>
-      <c r="I26" s="6">
-        <f t="shared" si="0"/>
-        <v>1075</v>
-      </c>
-      <c r="J26" s="6">
-        <f t="shared" si="1"/>
-        <v>365</v>
-      </c>
-      <c r="K26" s="11" t="s">
-        <v>6</v>
-      </c>
       <c r="L26" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>7</v>
       </c>
       <c r="N26" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
-        <v>46274</v>
+        <v>46269</v>
       </c>
       <c r="B27" s="11">
         <v>370</v>
       </c>
       <c r="C27" s="11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D27" s="11">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="E27" s="11">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F27" s="11">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G27" s="11">
+        <v>7</v>
+      </c>
+      <c r="H27" s="11">
+        <v>185</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="2"/>
+        <v>1145</v>
+      </c>
+      <c r="J27" s="6">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10">
+        <v>46270</v>
+      </c>
+      <c r="B28" s="11">
+        <v>450</v>
+      </c>
+      <c r="C28" s="11">
+        <v>60</v>
+      </c>
+      <c r="D28" s="11">
+        <v>100</v>
+      </c>
+      <c r="E28" s="11">
+        <v>100</v>
+      </c>
+      <c r="F28" s="11">
+        <v>50</v>
+      </c>
+      <c r="G28" s="11">
+        <v>1</v>
+      </c>
+      <c r="H28" s="11">
+        <v>195</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="2"/>
+        <v>955</v>
+      </c>
+      <c r="J28" s="6">
+        <f t="shared" si="3"/>
+        <v>485</v>
+      </c>
+      <c r="K28" s="11" t="s">
         <v>5</v>
-      </c>
-      <c r="H27" s="11">
-        <v>160</v>
-      </c>
-      <c r="I27" s="6">
-        <f t="shared" si="0"/>
-        <v>1125</v>
-      </c>
-      <c r="J27" s="6">
-        <f t="shared" si="1"/>
-        <v>315</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N27" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
-        <v>46275</v>
-      </c>
-      <c r="B28" s="11">
-        <v>300</v>
-      </c>
-      <c r="C28" s="11">
-        <v>50</v>
-      </c>
-      <c r="D28" s="11">
-        <v>110</v>
-      </c>
-      <c r="E28" s="11">
-        <v>95</v>
-      </c>
-      <c r="F28" s="11">
-        <v>370</v>
-      </c>
-      <c r="G28" s="11">
-        <v>6</v>
-      </c>
-      <c r="H28" s="11">
-        <v>185</v>
-      </c>
-      <c r="I28" s="6">
-        <f t="shared" si="0"/>
-        <v>1110</v>
-      </c>
-      <c r="J28" s="6">
-        <f t="shared" si="1"/>
-        <v>330</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>9</v>
       </c>
       <c r="L28" s="11" t="s">
         <v>28</v>
@@ -1830,153 +1854,153 @@
         <v>11</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
-        <v>46276</v>
+        <v>46271</v>
       </c>
       <c r="B29" s="11">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C29" s="11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D29" s="11">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="E29" s="11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F29" s="11">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="G29" s="11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="I29" s="6">
-        <f t="shared" si="0"/>
-        <v>1110</v>
+        <f t="shared" si="2"/>
+        <v>875</v>
       </c>
       <c r="J29" s="6">
-        <f t="shared" si="1"/>
-        <v>330</v>
+        <f t="shared" si="3"/>
+        <v>565</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>46277</v>
+        <v>46272</v>
       </c>
       <c r="B30" s="11">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="C30" s="11">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D30" s="11">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E30" s="11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F30" s="11">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G30" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H30" s="11">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="0"/>
-        <v>825</v>
+        <f t="shared" si="2"/>
+        <v>1160</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="1"/>
-        <v>615</v>
+        <f t="shared" si="3"/>
+        <v>280</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M30" s="11" t="s">
         <v>7</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
-        <v>46278</v>
+        <v>46273</v>
       </c>
       <c r="B31" s="11">
+        <v>280</v>
+      </c>
+      <c r="C31" s="11">
+        <v>70</v>
+      </c>
+      <c r="D31" s="11">
+        <v>150</v>
+      </c>
+      <c r="E31" s="11">
+        <v>100</v>
+      </c>
+      <c r="F31" s="11">
         <v>300</v>
       </c>
-      <c r="C31" s="11">
-        <v>80</v>
-      </c>
-      <c r="D31" s="11">
-        <v>105</v>
-      </c>
-      <c r="E31" s="11">
-        <v>85</v>
-      </c>
-      <c r="F31" s="11">
-        <v>0</v>
-      </c>
       <c r="G31" s="11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H31" s="11">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" si="0"/>
-        <v>780</v>
+        <f t="shared" si="2"/>
+        <v>1075</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="1"/>
-        <v>660</v>
+        <f t="shared" si="3"/>
+        <v>365</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B32" s="11">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="C32" s="11">
         <v>65</v>
@@ -1985,27 +2009,27 @@
         <v>120</v>
       </c>
       <c r="E32" s="11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F32" s="11">
-        <v>220</v>
+        <v>300</v>
       </c>
       <c r="G32" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="11">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="0"/>
-        <v>1085</v>
+        <f t="shared" si="2"/>
+        <v>1125</v>
       </c>
       <c r="J32" s="6">
-        <f t="shared" si="1"/>
-        <v>355</v>
+        <f t="shared" si="3"/>
+        <v>315</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L32" s="11" t="s">
         <v>10</v>
@@ -2014,44 +2038,44 @@
         <v>11</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="B33" s="11">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C33" s="11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D33" s="11">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E33" s="11">
         <v>95</v>
       </c>
       <c r="F33" s="11">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="G33" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33" s="11">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="0"/>
-        <v>1115</v>
+        <f t="shared" si="2"/>
+        <v>1110</v>
       </c>
       <c r="J33" s="6">
-        <f t="shared" si="1"/>
-        <v>325</v>
+        <f t="shared" si="3"/>
+        <v>330</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L33" s="11" t="s">
         <v>28</v>
@@ -2060,166 +2084,334 @@
         <v>11</v>
       </c>
       <c r="N33" s="14" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="B34" s="11">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="C34" s="11">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D34" s="11">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E34" s="11">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F34" s="11">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G34" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H34" s="11">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="I34" s="6">
-        <f t="shared" si="0"/>
-        <v>1220</v>
+        <f t="shared" si="2"/>
+        <v>1110</v>
       </c>
       <c r="J34" s="6">
-        <f t="shared" si="1"/>
-        <v>220</v>
+        <f t="shared" si="3"/>
+        <v>330</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L34" s="11" t="s">
         <v>10</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N34" s="14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
-        <v>46282</v>
-      </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="14"/>
+        <v>46277</v>
+      </c>
+      <c r="B35" s="11">
+        <v>350</v>
+      </c>
+      <c r="C35" s="11">
+        <v>75</v>
+      </c>
+      <c r="D35" s="11">
+        <v>115</v>
+      </c>
+      <c r="E35" s="11">
+        <v>90</v>
+      </c>
+      <c r="F35" s="11">
+        <v>0</v>
+      </c>
+      <c r="G35" s="11">
+        <v>0</v>
+      </c>
+      <c r="H35" s="11">
+        <v>195</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="2"/>
+        <v>825</v>
+      </c>
+      <c r="J35" s="6">
+        <f t="shared" si="3"/>
+        <v>615</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N35" s="14" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
-        <v>46283</v>
-      </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="14"/>
+        <v>46278</v>
+      </c>
+      <c r="B36" s="11">
+        <v>300</v>
+      </c>
+      <c r="C36" s="11">
+        <v>80</v>
+      </c>
+      <c r="D36" s="11">
+        <v>105</v>
+      </c>
+      <c r="E36" s="11">
+        <v>85</v>
+      </c>
+      <c r="F36" s="11">
+        <v>0</v>
+      </c>
+      <c r="G36" s="11">
+        <v>0</v>
+      </c>
+      <c r="H36" s="11">
+        <v>210</v>
+      </c>
+      <c r="I36" s="6">
+        <f t="shared" si="2"/>
+        <v>780</v>
+      </c>
+      <c r="J36" s="6">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
-        <v>46284</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="14"/>
+        <v>46279</v>
+      </c>
+      <c r="B37" s="11">
+        <v>400</v>
+      </c>
+      <c r="C37" s="11">
+        <v>65</v>
+      </c>
+      <c r="D37" s="11">
+        <v>120</v>
+      </c>
+      <c r="E37" s="11">
+        <v>100</v>
+      </c>
+      <c r="F37" s="11">
+        <v>220</v>
+      </c>
+      <c r="G37" s="11">
+        <v>4</v>
+      </c>
+      <c r="H37" s="11">
+        <v>180</v>
+      </c>
+      <c r="I37" s="6">
+        <f t="shared" si="2"/>
+        <v>1085</v>
+      </c>
+      <c r="J37" s="6">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
-        <v>46285</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="14"/>
+        <v>46280</v>
+      </c>
+      <c r="B38" s="11">
+        <v>360</v>
+      </c>
+      <c r="C38" s="11">
+        <v>60</v>
+      </c>
+      <c r="D38" s="11">
+        <v>125</v>
+      </c>
+      <c r="E38" s="11">
+        <v>95</v>
+      </c>
+      <c r="F38" s="11">
+        <v>300</v>
+      </c>
+      <c r="G38" s="11">
+        <v>5</v>
+      </c>
+      <c r="H38" s="11">
+        <v>175</v>
+      </c>
+      <c r="I38" s="6">
+        <f t="shared" si="2"/>
+        <v>1115</v>
+      </c>
+      <c r="J38" s="6">
+        <f t="shared" si="3"/>
+        <v>325</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N38" s="14" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
-        <v>46286</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="14"/>
+        <v>46281</v>
+      </c>
+      <c r="B39" s="11">
+        <v>390</v>
+      </c>
+      <c r="C39" s="11">
+        <v>70</v>
+      </c>
+      <c r="D39" s="11">
+        <v>130</v>
+      </c>
+      <c r="E39" s="11">
+        <v>90</v>
+      </c>
+      <c r="F39" s="11">
+        <v>350</v>
+      </c>
+      <c r="G39" s="11">
+        <v>5</v>
+      </c>
+      <c r="H39" s="11">
+        <v>190</v>
+      </c>
+      <c r="I39" s="6">
+        <f t="shared" si="2"/>
+        <v>1220</v>
+      </c>
+      <c r="J39" s="6">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N39" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
-        <v>46287</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="14"/>
+        <v>46282</v>
+      </c>
+      <c r="B40" s="11">
+        <v>400</v>
+      </c>
+      <c r="C40" s="11">
+        <v>75</v>
+      </c>
+      <c r="D40" s="11">
+        <v>140</v>
+      </c>
+      <c r="E40" s="11">
+        <v>80</v>
+      </c>
+      <c r="F40" s="11">
+        <v>360</v>
+      </c>
+      <c r="G40" s="11">
+        <v>6</v>
+      </c>
+      <c r="H40" s="11">
+        <v>170</v>
+      </c>
+      <c r="I40" s="6">
+        <f t="shared" si="2"/>
+        <v>1225</v>
+      </c>
+      <c r="J40" s="6">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N40" s="14" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
@@ -2237,7 +2429,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
-        <v>46289</v>
+        <v>46284</v>
       </c>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -2255,7 +2447,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
-        <v>46290</v>
+        <v>46285</v>
       </c>
       <c r="B43" s="11"/>
       <c r="C43" s="11"/>
@@ -2273,7 +2465,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
-        <v>46291</v>
+        <v>46286</v>
       </c>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -2291,7 +2483,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
-        <v>46292</v>
+        <v>46287</v>
       </c>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -2309,7 +2501,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -2326,25 +2518,116 @@
       <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C47" s="6"/>
+      <c r="A47" s="10">
+        <v>46289</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
       <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C48" s="6"/>
+      <c r="A48" s="10">
+        <v>46290</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
       <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="14"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>46291</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="14"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>46292</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="14"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="10">
+        <v>46293</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="14"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C52" s="6"/>
+      <c r="I52" s="6"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C53" s="6"/>
+      <c r="I53" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K46" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K51" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L46" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L51" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M46" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M51" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3728CF-DD34-442E-8B74-44F576491268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D7073F-7BE9-4C30-A07E-210CD0E82634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="66">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>FOCUSED MINDSET</t>
+  </si>
+  <si>
+    <t>PRACTICED FOR CA</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1058,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I40" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I41" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1151,7 +1154,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J40" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J41" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2413,19 +2416,47 @@
       <c r="A41" s="10">
         <v>46283</v>
       </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="14"/>
+      <c r="B41" s="11">
+        <v>350</v>
+      </c>
+      <c r="C41" s="11">
+        <v>65</v>
+      </c>
+      <c r="D41" s="11">
+        <v>160</v>
+      </c>
+      <c r="E41" s="11">
+        <v>90</v>
+      </c>
+      <c r="F41" s="11">
+        <v>420</v>
+      </c>
+      <c r="G41" s="11">
+        <v>7</v>
+      </c>
+      <c r="H41" s="11">
+        <v>155</v>
+      </c>
+      <c r="I41" s="6">
+        <f t="shared" si="2"/>
+        <v>1240</v>
+      </c>
+      <c r="J41" s="6">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D7073F-7BE9-4C30-A07E-210CD0E82634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530C2FFA-29DF-4202-8396-5DA3A7E734E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="67">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>PRACTICED FOR CA</t>
+  </si>
+  <si>
+    <t>MANAGED TASKS WELL</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1061,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I41" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I42" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1154,7 +1157,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J41" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J42" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2462,19 +2465,47 @@
       <c r="A42" s="10">
         <v>46284</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="14"/>
+      <c r="B42" s="11">
+        <v>400</v>
+      </c>
+      <c r="C42" s="11">
+        <v>60</v>
+      </c>
+      <c r="D42" s="11">
+        <v>135</v>
+      </c>
+      <c r="E42" s="11">
+        <v>100</v>
+      </c>
+      <c r="F42" s="11">
+        <v>50</v>
+      </c>
+      <c r="G42" s="11">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11">
+        <v>190</v>
+      </c>
+      <c r="I42" s="6">
+        <f t="shared" si="2"/>
+        <v>935</v>
+      </c>
+      <c r="J42" s="6">
+        <f t="shared" si="3"/>
+        <v>505</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N42" s="14" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530C2FFA-29DF-4202-8396-5DA3A7E734E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E796DC45-5AEB-4AC8-9335-A7CF03BDFEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="68">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>MANAGED TASKS WELL</t>
+  </si>
+  <si>
+    <t>SPENT WEEKEND WITH MY FAMILY</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1064,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I42" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I43" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1157,7 +1160,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J42" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J43" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2511,19 +2514,47 @@
       <c r="A43" s="10">
         <v>46285</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="14"/>
+      <c r="B43" s="11">
+        <v>480</v>
+      </c>
+      <c r="C43" s="11">
+        <v>70</v>
+      </c>
+      <c r="D43" s="11">
+        <v>120</v>
+      </c>
+      <c r="E43" s="11">
+        <v>95</v>
+      </c>
+      <c r="F43" s="11">
+        <v>0</v>
+      </c>
+      <c r="G43" s="11">
+        <v>0</v>
+      </c>
+      <c r="H43" s="11">
+        <v>185</v>
+      </c>
+      <c r="I43" s="6">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+      <c r="J43" s="6">
+        <f t="shared" si="3"/>
+        <v>490</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N43" s="14" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E796DC45-5AEB-4AC8-9335-A7CF03BDFEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC612113-FCA4-4F30-8095-1BC03F643774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>SPENT WEEKEND WITH MY FAMILY</t>
+  </si>
+  <si>
+    <t>DAY WENT WELL</t>
   </si>
 </sst>
 </file>
@@ -305,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -353,6 +356,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1064,7 +1076,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I43" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I44" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1160,7 +1172,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J43" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J44" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2560,145 +2572,159 @@
       <c r="A44" s="10">
         <v>46286</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="14"/>
+      <c r="B44" s="11">
+        <v>370</v>
+      </c>
+      <c r="C44" s="11">
+        <v>75</v>
+      </c>
+      <c r="D44" s="11">
+        <v>130</v>
+      </c>
+      <c r="E44" s="11">
+        <v>85</v>
+      </c>
+      <c r="F44" s="11">
+        <v>200</v>
+      </c>
+      <c r="G44" s="11">
+        <v>4</v>
+      </c>
+      <c r="H44" s="11">
+        <v>175</v>
+      </c>
+      <c r="I44" s="6">
+        <f t="shared" si="2"/>
+        <v>1035</v>
+      </c>
+      <c r="J44" s="6">
+        <f t="shared" si="3"/>
+        <v>405</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N44" s="14" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
-        <v>46287</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="14"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="20"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="10">
-        <v>46288</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="14"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="20"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="10">
-        <v>46289</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="14"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="20"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="10">
-        <v>46290</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="14"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="19"/>
+      <c r="N48" s="20"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="10">
-        <v>46291</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="14"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="20"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="10">
-        <v>46292</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="14"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="20"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="10">
-        <v>46293</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="14"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="20"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C52" s="6"/>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC612113-FCA4-4F30-8095-1BC03F643774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7405183-BC55-4A5F-A583-B58EFA2E1CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="70">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>DAY WENT WELL</t>
+  </si>
+  <si>
+    <t>REVISED DATABASE</t>
   </si>
 </sst>
 </file>
@@ -308,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -357,14 +360,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
@@ -1076,7 +1074,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I44" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I45" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1172,7 +1170,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J44" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J45" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2615,124 +2613,224 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="18"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="20"/>
+      <c r="A45" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B45" s="11">
+        <v>300</v>
+      </c>
+      <c r="C45" s="11">
+        <v>65</v>
+      </c>
+      <c r="D45" s="11">
+        <v>115</v>
+      </c>
+      <c r="E45" s="11">
+        <v>90</v>
+      </c>
+      <c r="F45" s="11">
+        <v>300</v>
+      </c>
+      <c r="G45" s="11">
+        <v>5</v>
+      </c>
+      <c r="H45" s="11">
+        <v>180</v>
+      </c>
+      <c r="I45" s="6">
+        <f t="shared" si="2"/>
+        <v>1050</v>
+      </c>
+      <c r="J45" s="6">
+        <f t="shared" si="3"/>
+        <v>390</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N45" s="14" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
+      <c r="A46" s="10">
+        <v>46288</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
       <c r="I46" s="6"/>
       <c r="J46" s="6"/>
-      <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="20"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="18"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
+      <c r="A47" s="10">
+        <v>46289</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="19"/>
-      <c r="N47" s="20"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
+      <c r="A48" s="10">
+        <v>46290</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="20"/>
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="14"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
+      <c r="A49" s="10">
+        <v>46291</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="20"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="14"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="18"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
+      <c r="A50" s="10">
+        <v>46292</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="20"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="14"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
+      <c r="A51" s="10">
+        <v>46293</v>
+      </c>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="20"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="14"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C52" s="6"/>
+      <c r="A52" s="10">
+        <v>46294</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
       <c r="I52" s="6"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="19"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C53" s="6"/>
+      <c r="A53" s="10">
+        <v>46295</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
       <c r="I53" s="6"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="19"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="10">
+        <v>46296</v>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="19"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="10">
+        <v>46297</v>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7405183-BC55-4A5F-A583-B58EFA2E1CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF822EF3-6B92-47AC-A5A5-58392F67F903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>REVISED DATABASE</t>
+  </si>
+  <si>
+    <t>AVERAGE DAY</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1077,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I45" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I46" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1170,7 +1173,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J45" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J46" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2662,19 +2665,47 @@
       <c r="A46" s="10">
         <v>46288</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="14"/>
+      <c r="B46" s="11">
+        <v>350</v>
+      </c>
+      <c r="C46" s="11">
+        <v>55</v>
+      </c>
+      <c r="D46" s="11">
+        <v>100</v>
+      </c>
+      <c r="E46" s="11">
+        <v>90</v>
+      </c>
+      <c r="F46" s="11">
+        <v>300</v>
+      </c>
+      <c r="G46" s="11">
+        <v>5</v>
+      </c>
+      <c r="H46" s="11">
+        <v>190</v>
+      </c>
+      <c r="I46" s="6">
+        <f t="shared" si="2"/>
+        <v>1085</v>
+      </c>
+      <c r="J46" s="6">
+        <f t="shared" si="3"/>
+        <v>355</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N46" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF822EF3-6B92-47AC-A5A5-58392F67F903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDF5D3A-1BDD-4427-9D39-C9315A1E6DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="72">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>AVERAGE DAY</t>
+  </si>
+  <si>
+    <t>STUDIED FOR CA</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1080,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I46" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I47" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1173,7 +1176,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J46" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J47" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2711,19 +2714,47 @@
       <c r="A47" s="10">
         <v>46289</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="14"/>
+      <c r="B47" s="11">
+        <v>350</v>
+      </c>
+      <c r="C47" s="11">
+        <v>70</v>
+      </c>
+      <c r="D47" s="11">
+        <v>130</v>
+      </c>
+      <c r="E47" s="11">
+        <v>85</v>
+      </c>
+      <c r="F47" s="11">
+        <v>360</v>
+      </c>
+      <c r="G47" s="11">
+        <v>6</v>
+      </c>
+      <c r="H47" s="11">
+        <v>185</v>
+      </c>
+      <c r="I47" s="6">
+        <f t="shared" si="2"/>
+        <v>1180</v>
+      </c>
+      <c r="J47" s="6">
+        <f t="shared" si="3"/>
+        <v>260</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N47" s="14" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DDF5D3A-1BDD-4427-9D39-C9315A1E6DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40CCB6C-2F7B-4E7E-9DF4-80C60D6136F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>STUDIED FOR CA</t>
+  </si>
+  <si>
+    <t>TOTALLY DRAINED</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1083,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" ref="I11:I47" si="2">SUM(B11:F11,H11)</f>
+        <f t="shared" ref="I11:I48" si="2">SUM(B11:F11,H11)</f>
         <v>1090</v>
       </c>
       <c r="J11" s="5">
@@ -1176,7 +1179,7 @@
         <v>1115</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" ref="J13:J47" si="3">1440-I13</f>
+        <f t="shared" ref="J13:J48" si="3">1440-I13</f>
         <v>325</v>
       </c>
       <c r="K13" s="11" t="s">
@@ -2760,19 +2763,47 @@
       <c r="A48" s="10">
         <v>46290</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="14"/>
+      <c r="B48" s="11">
+        <v>320</v>
+      </c>
+      <c r="C48" s="11">
+        <v>80</v>
+      </c>
+      <c r="D48" s="11">
+        <v>95</v>
+      </c>
+      <c r="E48" s="11">
+        <v>95</v>
+      </c>
+      <c r="F48" s="11">
+        <v>420</v>
+      </c>
+      <c r="G48" s="11">
+        <v>7</v>
+      </c>
+      <c r="H48" s="11">
+        <v>180</v>
+      </c>
+      <c r="I48" s="6">
+        <f t="shared" si="2"/>
+        <v>1190</v>
+      </c>
+      <c r="J48" s="6">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N48" s="14" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40CCB6C-2F7B-4E7E-9DF4-80C60D6136F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F768A8A-22C8-4E51-B0EF-8B5E7A9B78B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="70">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -215,18 +215,6 @@
     <t>BLISSFUL DAY</t>
   </si>
   <si>
-    <t>BALANCED ROUTINE</t>
-  </si>
-  <si>
-    <t>RECOVERY SUNDAY</t>
-  </si>
-  <si>
-    <t>STEADY STUDYING</t>
-  </si>
-  <si>
-    <t>LIGHT LOAD DAY</t>
-  </si>
-  <si>
     <t>EFFICIENT WORKFLOW</t>
   </si>
   <si>
@@ -255,6 +243,9 @@
   </si>
   <si>
     <t>TOTALLY DRAINED</t>
+  </si>
+  <si>
+    <t>DID MINOR PROJECT</t>
   </si>
 </sst>
 </file>
@@ -687,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
@@ -783,407 +774,407 @@
     </row>
     <row r="5" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B5" s="13">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="C5" s="13">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D5" s="13">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E5" s="13">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F5" s="13">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G5" s="13">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5" s="13">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="I5" s="17">
-        <f>SUM(B5:F5,H5)</f>
-        <v>1285</v>
+        <f t="shared" ref="I5" si="0">SUM(B5:F5,H5)</f>
+        <v>955</v>
       </c>
       <c r="J5" s="17">
-        <f>1440-I5</f>
-        <v>155</v>
+        <f t="shared" ref="J5" si="1">1440-I5</f>
+        <v>485</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N5" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16">
-        <v>46248</v>
-      </c>
-      <c r="B6" s="13">
+    <row r="6" spans="1:14" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>46252</v>
+      </c>
+      <c r="B6" s="12">
+        <v>420</v>
+      </c>
+      <c r="C6" s="12">
+        <v>60</v>
+      </c>
+      <c r="D6" s="12">
+        <v>90</v>
+      </c>
+      <c r="E6" s="12">
+        <v>75</v>
+      </c>
+      <c r="F6" s="12">
+        <v>300</v>
+      </c>
+      <c r="G6" s="12">
+        <v>6</v>
+      </c>
+      <c r="H6" s="12">
+        <v>90</v>
+      </c>
+      <c r="I6" s="5">
+        <f>SUM(B6:F6,H6)</f>
+        <v>1035</v>
+      </c>
+      <c r="J6" s="5">
+        <f>1440-I6</f>
+        <v>405</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>46253</v>
+      </c>
+      <c r="B7" s="12">
         <v>360</v>
       </c>
-      <c r="C6" s="13">
-        <v>45</v>
-      </c>
-      <c r="D6" s="13">
-        <v>160</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="C7" s="12">
+        <v>40</v>
+      </c>
+      <c r="D7" s="12">
+        <v>80</v>
+      </c>
+      <c r="E7" s="12">
+        <v>90</v>
+      </c>
+      <c r="F7" s="12">
+        <v>400</v>
+      </c>
+      <c r="G7" s="12">
+        <v>7</v>
+      </c>
+      <c r="H7" s="12">
+        <v>120</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" ref="I7:I45" si="2">SUM(B7:F7,H7)</f>
+        <v>1090</v>
+      </c>
+      <c r="J7" s="5">
+        <f>1440-I7</f>
+        <v>350</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>46254</v>
+      </c>
+      <c r="B8" s="11">
+        <v>390</v>
+      </c>
+      <c r="C8" s="11">
+        <v>55</v>
+      </c>
+      <c r="D8" s="11">
+        <v>75</v>
+      </c>
+      <c r="E8" s="11">
         <v>60</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F8" s="11">
+        <v>450</v>
+      </c>
+      <c r="G8" s="11">
+        <v>8</v>
+      </c>
+      <c r="H8" s="11">
+        <v>100</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="2"/>
+        <v>1130</v>
+      </c>
+      <c r="J8" s="5">
+        <f>1440-I8</f>
+        <v>310</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>46255</v>
+      </c>
+      <c r="B9" s="11">
+        <v>400</v>
+      </c>
+      <c r="C9" s="11">
+        <v>60</v>
+      </c>
+      <c r="D9" s="11">
+        <v>100</v>
+      </c>
+      <c r="E9" s="11">
+        <v>55</v>
+      </c>
+      <c r="F9" s="11">
         <v>350</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G9" s="11">
         <v>7</v>
       </c>
-      <c r="H6" s="13">
-        <v>120</v>
-      </c>
-      <c r="I6" s="17">
-        <f t="shared" ref="I6:I9" si="0">SUM(B6:F6,H6)</f>
-        <v>1095</v>
-      </c>
-      <c r="J6" s="17">
-        <f t="shared" ref="J6:J9" si="1">1440-I6</f>
-        <v>345</v>
-      </c>
-      <c r="K6" s="13" t="s">
+      <c r="H9" s="11">
+        <v>150</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="2"/>
+        <v>1115</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" ref="J9:J45" si="3">1440-I9</f>
+        <v>325</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
+        <v>46256</v>
+      </c>
+      <c r="B10" s="11">
+        <v>480</v>
+      </c>
+      <c r="C10" s="11">
+        <v>40</v>
+      </c>
+      <c r="D10" s="11">
+        <v>85</v>
+      </c>
+      <c r="E10" s="11">
+        <v>80</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>170</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="2"/>
+        <v>855</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="3"/>
+        <v>585</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>46257</v>
+      </c>
+      <c r="B11" s="11">
+        <v>450</v>
+      </c>
+      <c r="C11" s="11">
+        <v>50</v>
+      </c>
+      <c r="D11" s="11">
+        <v>150</v>
+      </c>
+      <c r="E11" s="11">
+        <v>150</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <v>250</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>1050</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="3"/>
+        <v>390</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N6" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16">
-        <v>46249</v>
-      </c>
-      <c r="B7" s="13">
-        <v>450</v>
-      </c>
-      <c r="C7" s="13">
-        <v>75</v>
-      </c>
-      <c r="D7" s="13">
-        <v>90</v>
-      </c>
-      <c r="E7" s="13">
-        <v>100</v>
-      </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
-        <v>200</v>
-      </c>
-      <c r="I7" s="17">
-        <f t="shared" si="0"/>
-        <v>915</v>
-      </c>
-      <c r="J7" s="17">
-        <f t="shared" si="1"/>
-        <v>525</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
-        <v>46250</v>
-      </c>
-      <c r="B8" s="13">
-        <v>480</v>
-      </c>
-      <c r="C8" s="13">
-        <v>60</v>
-      </c>
-      <c r="D8" s="13">
-        <v>110</v>
-      </c>
-      <c r="E8" s="13">
-        <v>80</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>180</v>
-      </c>
-      <c r="I8" s="17">
-        <f t="shared" si="0"/>
-        <v>910</v>
-      </c>
-      <c r="J8" s="17">
-        <f t="shared" si="1"/>
-        <v>530</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16">
-        <v>46251</v>
-      </c>
-      <c r="B9" s="13">
-        <v>390</v>
-      </c>
-      <c r="C9" s="13">
-        <v>65</v>
-      </c>
-      <c r="D9" s="13">
-        <v>105</v>
-      </c>
-      <c r="E9" s="13">
-        <v>85</v>
-      </c>
-      <c r="F9" s="13">
-        <v>200</v>
-      </c>
-      <c r="G9" s="13">
-        <v>4</v>
-      </c>
-      <c r="H9" s="13">
-        <v>110</v>
-      </c>
-      <c r="I9" s="17">
-        <f t="shared" si="0"/>
-        <v>955</v>
-      </c>
-      <c r="J9" s="17">
-        <f t="shared" si="1"/>
-        <v>485</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
-        <v>46252</v>
-      </c>
-      <c r="B10" s="12">
-        <v>420</v>
-      </c>
-      <c r="C10" s="12">
-        <v>60</v>
-      </c>
-      <c r="D10" s="12">
-        <v>90</v>
-      </c>
-      <c r="E10" s="12">
-        <v>75</v>
-      </c>
-      <c r="F10" s="12">
-        <v>300</v>
-      </c>
-      <c r="G10" s="12">
-        <v>6</v>
-      </c>
-      <c r="H10" s="12">
-        <v>90</v>
-      </c>
-      <c r="I10" s="5">
-        <f>SUM(B10:F10,H10)</f>
-        <v>1035</v>
-      </c>
-      <c r="J10" s="5">
-        <f>1440-I10</f>
-        <v>405</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
-        <v>46253</v>
-      </c>
-      <c r="B11" s="12">
-        <v>360</v>
-      </c>
-      <c r="C11" s="12">
-        <v>40</v>
-      </c>
-      <c r="D11" s="12">
-        <v>80</v>
-      </c>
-      <c r="E11" s="12">
-        <v>90</v>
-      </c>
-      <c r="F11" s="12">
+      <c r="N11" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="11">
         <v>400</v>
-      </c>
-      <c r="G11" s="12">
-        <v>7</v>
-      </c>
-      <c r="H11" s="12">
-        <v>120</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" ref="I11:I48" si="2">SUM(B11:F11,H11)</f>
-        <v>1090</v>
-      </c>
-      <c r="J11" s="5">
-        <f>1440-I11</f>
-        <v>350</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
-        <v>46254</v>
-      </c>
-      <c r="B12" s="11">
-        <v>390</v>
       </c>
       <c r="C12" s="11">
         <v>55</v>
       </c>
       <c r="D12" s="11">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="E12" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F12" s="11">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="G12" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H12" s="11">
-        <v>100</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="2"/>
-        <v>1130</v>
-      </c>
-      <c r="J12" s="5">
-        <f>1440-I12</f>
-        <v>310</v>
+        <v>200</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="2"/>
+        <v>1110</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="3"/>
+        <v>330</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>10</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B13" s="11">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="C13" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D13" s="11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E13" s="11">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="F13" s="11">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G13" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="11">
-        <v>150</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="2"/>
-        <v>1115</v>
-      </c>
-      <c r="J13" s="5">
-        <f t="shared" ref="J13:J48" si="3">1440-I13</f>
-        <v>325</v>
+        <v>190</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="2"/>
+        <v>1100</v>
+      </c>
+      <c r="J13" s="6">
+        <f t="shared" si="3"/>
+        <v>340</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>28</v>
@@ -1192,21 +1183,21 @@
         <v>7</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B14" s="11">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C14" s="11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D14" s="11">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="E14" s="11">
         <v>80</v>
@@ -1218,110 +1209,110 @@
         <v>0</v>
       </c>
       <c r="H14" s="11">
-        <v>170</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="2"/>
-        <v>855</v>
-      </c>
-      <c r="J14" s="5">
-        <f t="shared" si="3"/>
-        <v>585</v>
+        <v>200</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="2"/>
+        <v>970</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" si="3"/>
+        <v>470</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B15" s="11">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="C15" s="11">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D15" s="11">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E15" s="11">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="F15" s="11">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H15" s="11">
-        <v>250</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="2"/>
-        <v>1050</v>
-      </c>
-      <c r="J15" s="5">
-        <f t="shared" si="3"/>
-        <v>390</v>
+        <v>160</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="2"/>
+        <v>1090</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" si="3"/>
+        <v>350</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>6</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B16" s="11">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C16" s="11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D16" s="11">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="E16" s="11">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F16" s="11">
         <v>200</v>
       </c>
       <c r="G16" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="11">
         <v>200</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>900</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="3"/>
-        <v>330</v>
+        <v>540</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="L16" s="11" t="s">
         <v>10</v>
@@ -1330,70 +1321,70 @@
         <v>11</v>
       </c>
       <c r="N16" s="14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B17" s="11">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="C17" s="11">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D17" s="11">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E17" s="11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F17" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G17" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="11">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="2"/>
-        <v>1100</v>
+        <v>815</v>
       </c>
       <c r="J17" s="6">
         <f t="shared" si="3"/>
-        <v>340</v>
+        <v>625</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>7</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B18" s="11">
-        <v>470</v>
+        <v>420</v>
       </c>
       <c r="C18" s="11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D18" s="11">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="E18" s="11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F18" s="11">
         <v>0</v>
@@ -1402,153 +1393,153 @@
         <v>0</v>
       </c>
       <c r="H18" s="11">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I18" s="6">
         <f t="shared" si="2"/>
-        <v>970</v>
+        <v>875</v>
       </c>
       <c r="J18" s="6">
         <f t="shared" si="3"/>
-        <v>470</v>
+        <v>565</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>11</v>
       </c>
       <c r="N18" s="14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B19" s="11">
-        <v>320</v>
+        <v>430</v>
       </c>
       <c r="C19" s="11">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D19" s="11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E19" s="11">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="F19" s="11">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G19" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H19" s="11">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="2"/>
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="J19" s="6">
         <f t="shared" si="3"/>
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>27</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B20" s="11">
         <v>300</v>
       </c>
       <c r="C20" s="11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D20" s="11">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E20" s="11">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="F20" s="11">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G20" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="11">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>1030</v>
       </c>
       <c r="J20" s="6">
         <f t="shared" si="3"/>
-        <v>540</v>
+        <v>410</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>11</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="B21" s="11">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="C21" s="11">
         <v>40</v>
       </c>
       <c r="D21" s="11">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E21" s="11">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="F21" s="11">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G21" s="11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" s="11">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="2"/>
-        <v>815</v>
+        <v>1125</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="3"/>
-        <v>625</v>
+        <v>315</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>38</v>
@@ -1557,44 +1548,44 @@
         <v>29</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="B22" s="11">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="C22" s="11">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D22" s="11">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="E22" s="11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F22" s="11">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G22" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22" s="11">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="I22" s="6">
         <f t="shared" si="2"/>
-        <v>875</v>
+        <v>1030</v>
       </c>
       <c r="J22" s="6">
         <f t="shared" si="3"/>
-        <v>565</v>
+        <v>410</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>5</v>
@@ -1603,93 +1594,93 @@
         <v>10</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B23" s="11">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="C23" s="11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D23" s="11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E23" s="11">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F23" s="11">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G23" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H23" s="11">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I23" s="6">
         <f t="shared" si="2"/>
-        <v>1080</v>
+        <v>1145</v>
       </c>
       <c r="J23" s="6">
         <f t="shared" si="3"/>
-        <v>360</v>
+        <v>295</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B24" s="11">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="C24" s="11">
         <v>60</v>
       </c>
       <c r="D24" s="11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E24" s="11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F24" s="11">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11">
+        <v>195</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="2"/>
+        <v>955</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="3"/>
+        <v>485</v>
+      </c>
+      <c r="K24" s="11" t="s">
         <v>5</v>
-      </c>
-      <c r="H24" s="11">
-        <v>180</v>
-      </c>
-      <c r="I24" s="6">
-        <f t="shared" si="2"/>
-        <v>1030</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="3"/>
-        <v>410</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="L24" s="11" t="s">
         <v>28</v>
@@ -1698,90 +1689,90 @@
         <v>11</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="B25" s="11">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="C25" s="11">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D25" s="11">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="E25" s="11">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F25" s="11">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G25" s="11">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11">
+        <v>180</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="2"/>
+        <v>875</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+      <c r="K25" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="11">
-        <v>175</v>
-      </c>
-      <c r="I25" s="6">
-        <f t="shared" si="2"/>
-        <v>1125</v>
-      </c>
-      <c r="J25" s="6">
-        <f t="shared" si="3"/>
-        <v>315</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>38</v>
-      </c>
       <c r="L25" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B26" s="11">
-        <v>330</v>
+        <v>400</v>
       </c>
       <c r="C26" s="11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D26" s="11">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="E26" s="11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F26" s="11">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G26" s="11">
         <v>6</v>
       </c>
       <c r="H26" s="11">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="2"/>
-        <v>1030</v>
+        <v>1160</v>
       </c>
       <c r="J26" s="6">
         <f t="shared" si="3"/>
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L26" s="11" t="s">
         <v>10</v>
@@ -1790,41 +1781,41 @@
         <v>7</v>
       </c>
       <c r="N26" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B27" s="11">
-        <v>370</v>
+        <v>280</v>
       </c>
       <c r="C27" s="11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D27" s="11">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="E27" s="11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F27" s="11">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G27" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H27" s="11">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="2"/>
-        <v>1145</v>
+        <v>1075</v>
       </c>
       <c r="J27" s="6">
         <f t="shared" si="3"/>
-        <v>295</v>
+        <v>365</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>6</v>
@@ -1836,90 +1827,90 @@
         <v>7</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B28" s="11">
-        <v>450</v>
+        <v>370</v>
       </c>
       <c r="C28" s="11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D28" s="11">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E28" s="11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F28" s="11">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G28" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H28" s="11">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="2"/>
-        <v>955</v>
+        <v>1125</v>
       </c>
       <c r="J28" s="6">
         <f t="shared" si="3"/>
-        <v>485</v>
+        <v>315</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>5</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>11</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="6" customFormat="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B29" s="11">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C29" s="11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D29" s="11">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="E29" s="11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F29" s="11">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="G29" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H29" s="11">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" si="2"/>
-        <v>875</v>
+        <v>1110</v>
       </c>
       <c r="J29" s="6">
         <f t="shared" si="3"/>
-        <v>565</v>
+        <v>330</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L29" s="11" t="s">
         <v>28</v>
@@ -1928,44 +1919,44 @@
         <v>11</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B30" s="11">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="C30" s="11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D30" s="11">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E30" s="11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F30" s="11">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="G30" s="11">
         <v>6</v>
       </c>
       <c r="H30" s="11">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I30" s="6">
         <f t="shared" si="2"/>
-        <v>1160</v>
+        <v>1110</v>
       </c>
       <c r="J30" s="6">
         <f t="shared" si="3"/>
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L30" s="11" t="s">
         <v>10</v>
@@ -1974,44 +1965,44 @@
         <v>7</v>
       </c>
       <c r="N30" s="14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B31" s="11">
-        <v>280</v>
+        <v>350</v>
       </c>
       <c r="C31" s="11">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D31" s="11">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E31" s="11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F31" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G31" s="11">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>195</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="2"/>
+        <v>825</v>
+      </c>
+      <c r="J31" s="6">
+        <f t="shared" si="3"/>
+        <v>615</v>
+      </c>
+      <c r="K31" s="11" t="s">
         <v>5</v>
-      </c>
-      <c r="H31" s="11">
-        <v>175</v>
-      </c>
-      <c r="I31" s="6">
-        <f t="shared" si="2"/>
-        <v>1075</v>
-      </c>
-      <c r="J31" s="6">
-        <f t="shared" si="3"/>
-        <v>365</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="L31" s="11" t="s">
         <v>6</v>
@@ -2020,363 +2011,363 @@
         <v>7</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B32" s="11">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="C32" s="11">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D32" s="11">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E32" s="11">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F32" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G32" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="11">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="2"/>
-        <v>1125</v>
+        <v>780</v>
       </c>
       <c r="J32" s="6">
         <f t="shared" si="3"/>
-        <v>315</v>
+        <v>660</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N32" s="14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B33" s="11">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C33" s="11">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D33" s="11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E33" s="11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F33" s="11">
-        <v>370</v>
+        <v>220</v>
       </c>
       <c r="G33" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H33" s="11">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1085</v>
       </c>
       <c r="J33" s="6">
         <f t="shared" si="3"/>
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>9</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M33" s="11" t="s">
         <v>11</v>
       </c>
       <c r="N33" s="14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B34" s="11">
-        <v>320</v>
+        <v>360</v>
       </c>
       <c r="C34" s="11">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D34" s="11">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E34" s="11">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F34" s="11">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G34" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H34" s="11">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="J34" s="6">
         <f t="shared" si="3"/>
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N34" s="14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B35" s="11">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C35" s="11">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D35" s="11">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="E35" s="11">
         <v>90</v>
       </c>
       <c r="F35" s="11">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G35" s="11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H35" s="11">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="2"/>
-        <v>825</v>
+        <v>1220</v>
       </c>
       <c r="J35" s="6">
         <f t="shared" si="3"/>
-        <v>615</v>
+        <v>220</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>5</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N35" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="B36" s="11">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C36" s="11">
+        <v>75</v>
+      </c>
+      <c r="D36" s="11">
+        <v>140</v>
+      </c>
+      <c r="E36" s="11">
         <v>80</v>
       </c>
-      <c r="D36" s="11">
-        <v>105</v>
-      </c>
-      <c r="E36" s="11">
-        <v>85</v>
-      </c>
       <c r="F36" s="11">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G36" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36" s="11">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="2"/>
-        <v>780</v>
+        <v>1225</v>
       </c>
       <c r="J36" s="6">
         <f t="shared" si="3"/>
-        <v>660</v>
+        <v>215</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="N36" s="14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B37" s="11">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C37" s="11">
         <v>65</v>
       </c>
       <c r="D37" s="11">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="E37" s="11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F37" s="11">
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="G37" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H37" s="11">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="2"/>
-        <v>1085</v>
+        <v>1240</v>
       </c>
       <c r="J37" s="6">
         <f t="shared" si="3"/>
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N37" s="14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
-        <v>46280</v>
+        <v>46284</v>
       </c>
       <c r="B38" s="11">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C38" s="11">
         <v>60</v>
       </c>
       <c r="D38" s="11">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E38" s="11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F38" s="11">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G38" s="11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H38" s="11">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I38" s="6">
         <f t="shared" si="2"/>
-        <v>1115</v>
+        <v>935</v>
       </c>
       <c r="J38" s="6">
         <f t="shared" si="3"/>
-        <v>325</v>
+        <v>505</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>5</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N38" s="14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="B39" s="11">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="C39" s="11">
         <v>70</v>
       </c>
       <c r="D39" s="11">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E39" s="11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F39" s="11">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G39" s="11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="11">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I39" s="6">
         <f t="shared" si="2"/>
-        <v>1220</v>
+        <v>950</v>
       </c>
       <c r="J39" s="6">
         <f t="shared" si="3"/>
-        <v>220</v>
+        <v>490</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>5</v>
@@ -2388,50 +2379,50 @@
         <v>11</v>
       </c>
       <c r="N39" s="14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B40" s="11">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="C40" s="11">
         <v>75</v>
       </c>
       <c r="D40" s="11">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E40" s="11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F40" s="11">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="G40" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H40" s="11">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="I40" s="6">
         <f t="shared" si="2"/>
-        <v>1225</v>
+        <v>1035</v>
       </c>
       <c r="J40" s="6">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>405</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>9</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M40" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N40" s="14" t="s">
         <v>64</v>
@@ -2439,45 +2430,45 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B41" s="11">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C41" s="11">
         <v>65</v>
       </c>
       <c r="D41" s="11">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="E41" s="11">
         <v>90</v>
       </c>
       <c r="F41" s="11">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="G41" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H41" s="11">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="2"/>
-        <v>1240</v>
+        <v>1050</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>390</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>6</v>
       </c>
       <c r="M41" s="11" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="N41" s="14" t="s">
         <v>65</v>
@@ -2485,36 +2476,36 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
-        <v>46284</v>
+        <v>46288</v>
       </c>
       <c r="B42" s="11">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C42" s="11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D42" s="11">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="E42" s="11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F42" s="11">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G42" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H42" s="11">
         <v>190</v>
       </c>
       <c r="I42" s="6">
         <f t="shared" si="2"/>
-        <v>935</v>
+        <v>1085</v>
       </c>
       <c r="J42" s="6">
         <f t="shared" si="3"/>
-        <v>505</v>
+        <v>355</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>5</v>
@@ -2531,42 +2522,42 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
-        <v>46285</v>
+        <v>46289</v>
       </c>
       <c r="B43" s="11">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="C43" s="11">
         <v>70</v>
       </c>
       <c r="D43" s="11">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E43" s="11">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F43" s="11">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G43" s="11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H43" s="11">
         <v>185</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="2"/>
-        <v>950</v>
+        <v>1180</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="3"/>
-        <v>490</v>
+        <v>260</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M43" s="11" t="s">
         <v>11</v>
@@ -2577,45 +2568,45 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B44" s="11">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="C44" s="11">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D44" s="11">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E44" s="11">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F44" s="11">
-        <v>200</v>
+        <v>420</v>
       </c>
       <c r="G44" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H44" s="11">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="2"/>
-        <v>1035</v>
+        <v>1190</v>
       </c>
       <c r="J44" s="6">
         <f t="shared" si="3"/>
-        <v>405</v>
+        <v>250</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N44" s="14" t="s">
         <v>68</v>
@@ -2623,45 +2614,45 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
-        <v>46287</v>
+        <v>46291</v>
       </c>
       <c r="B45" s="11">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C45" s="11">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D45" s="11">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="E45" s="11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="F45" s="11">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G45" s="11">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11">
+        <v>200</v>
+      </c>
+      <c r="I45" s="6">
+        <f t="shared" si="2"/>
+        <v>920</v>
+      </c>
+      <c r="J45" s="6">
+        <f t="shared" si="3"/>
+        <v>520</v>
+      </c>
+      <c r="K45" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="11">
-        <v>180</v>
-      </c>
-      <c r="I45" s="6">
-        <f t="shared" si="2"/>
-        <v>1050</v>
-      </c>
-      <c r="J45" s="6">
-        <f t="shared" si="3"/>
-        <v>390</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>6</v>
-      </c>
       <c r="L45" s="11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M45" s="11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N45" s="14" t="s">
         <v>69</v>
@@ -2669,271 +2660,115 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
-        <v>46288</v>
-      </c>
-      <c r="B46" s="11">
-        <v>350</v>
-      </c>
-      <c r="C46" s="11">
-        <v>55</v>
-      </c>
-      <c r="D46" s="11">
-        <v>100</v>
-      </c>
-      <c r="E46" s="11">
-        <v>90</v>
-      </c>
-      <c r="F46" s="11">
-        <v>300</v>
-      </c>
-      <c r="G46" s="11">
-        <v>5</v>
-      </c>
-      <c r="H46" s="11">
-        <v>190</v>
-      </c>
-      <c r="I46" s="6">
-        <f t="shared" si="2"/>
-        <v>1085</v>
-      </c>
-      <c r="J46" s="6">
-        <f t="shared" si="3"/>
-        <v>355</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="N46" s="14" t="s">
-        <v>70</v>
-      </c>
+        <v>46292</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
-        <v>46289</v>
-      </c>
-      <c r="B47" s="11">
-        <v>350</v>
-      </c>
-      <c r="C47" s="11">
-        <v>70</v>
-      </c>
-      <c r="D47" s="11">
-        <v>130</v>
-      </c>
-      <c r="E47" s="11">
-        <v>85</v>
-      </c>
-      <c r="F47" s="11">
-        <v>360</v>
-      </c>
-      <c r="G47" s="11">
-        <v>6</v>
-      </c>
-      <c r="H47" s="11">
-        <v>185</v>
-      </c>
-      <c r="I47" s="6">
-        <f t="shared" si="2"/>
-        <v>1180</v>
-      </c>
-      <c r="J47" s="6">
-        <f t="shared" si="3"/>
-        <v>260</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="M47" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N47" s="14" t="s">
-        <v>71</v>
-      </c>
+        <v>46293</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
-        <v>46290</v>
-      </c>
-      <c r="B48" s="11">
-        <v>320</v>
-      </c>
-      <c r="C48" s="11">
-        <v>80</v>
-      </c>
-      <c r="D48" s="11">
-        <v>95</v>
-      </c>
-      <c r="E48" s="11">
-        <v>95</v>
-      </c>
-      <c r="F48" s="11">
-        <v>420</v>
-      </c>
-      <c r="G48" s="11">
-        <v>7</v>
-      </c>
-      <c r="H48" s="11">
-        <v>180</v>
-      </c>
-      <c r="I48" s="6">
-        <f t="shared" si="2"/>
-        <v>1190</v>
-      </c>
-      <c r="J48" s="6">
-        <f t="shared" si="3"/>
-        <v>250</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="L48" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="M48" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="N48" s="14" t="s">
-        <v>72</v>
-      </c>
+        <v>46294</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="6"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="19"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
-        <v>46291</v>
-      </c>
-      <c r="B49" s="11"/>
+        <v>46295</v>
+      </c>
+      <c r="B49" s="18"/>
       <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
       <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="14"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="19"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
-        <v>46292</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="14"/>
+        <v>46296</v>
+      </c>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="19"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
-        <v>46293</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="14"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="10">
-        <v>46294</v>
-      </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="18"/>
-      <c r="I52" s="6"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
-      <c r="N52" s="19"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="10">
-        <v>46295</v>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="18"/>
-      <c r="I53" s="6"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="19"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="10">
-        <v>46296</v>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="19"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="10">
         <v>46297</v>
       </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
-      <c r="N55" s="19"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K51" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K47" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L51" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L47" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M51" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M47" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F768A8A-22C8-4E51-B0EF-8B5E7A9B78B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED128D-ACA3-484A-B5F6-79D468E986D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>DID MINOR PROJECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTURBED  </t>
   </si>
 </sst>
 </file>
@@ -890,7 +893,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I45" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I46" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -986,7 +989,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J45" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J46" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2662,19 +2665,47 @@
       <c r="A46" s="10">
         <v>46292</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="14"/>
+      <c r="B46" s="11">
+        <v>360</v>
+      </c>
+      <c r="C46" s="11">
+        <v>60</v>
+      </c>
+      <c r="D46" s="11">
+        <v>120</v>
+      </c>
+      <c r="E46" s="11">
+        <v>80</v>
+      </c>
+      <c r="F46" s="11">
+        <v>0</v>
+      </c>
+      <c r="G46" s="11">
+        <v>0</v>
+      </c>
+      <c r="H46" s="11">
+        <v>210</v>
+      </c>
+      <c r="I46" s="6">
+        <f t="shared" si="2"/>
+        <v>830</v>
+      </c>
+      <c r="J46" s="6">
+        <f t="shared" si="3"/>
+        <v>610</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N46" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED128D-ACA3-484A-B5F6-79D468E986D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E9B648-43ED-4FFE-AE49-BDD1E0F337CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="72">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t xml:space="preserve">DISTURBED  </t>
+  </si>
+  <si>
+    <t>COMPLETED MINOR PROJECT</t>
   </si>
 </sst>
 </file>
@@ -893,7 +896,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I46" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I47" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -989,7 +992,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J46" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J47" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2711,19 +2714,47 @@
       <c r="A47" s="10">
         <v>46293</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="14"/>
+      <c r="B47" s="11">
+        <v>420</v>
+      </c>
+      <c r="C47" s="11">
+        <v>75</v>
+      </c>
+      <c r="D47" s="11">
+        <v>150</v>
+      </c>
+      <c r="E47" s="11">
+        <v>110</v>
+      </c>
+      <c r="F47" s="11">
+        <v>0</v>
+      </c>
+      <c r="G47" s="11">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11">
+        <v>195</v>
+      </c>
+      <c r="I47" s="6">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+      <c r="J47" s="6">
+        <f t="shared" si="3"/>
+        <v>490</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N47" s="14" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E9B648-43ED-4FFE-AE49-BDD1E0F337CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D070A4E-6B7C-4AB0-BD37-2EA2E882CA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>COMPLETED MINOR PROJECT</t>
+  </si>
+  <si>
+    <t>REVISION DAY</t>
   </si>
 </sst>
 </file>
@@ -896,7 +899,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I47" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I48" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -992,7 +995,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J47" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J48" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2760,18 +2763,47 @@
       <c r="A48" s="10">
         <v>46294</v>
       </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="18"/>
-      <c r="I48" s="6"/>
-      <c r="K48" s="18"/>
-      <c r="L48" s="18"/>
-      <c r="M48" s="18"/>
-      <c r="N48" s="19"/>
+      <c r="B48" s="12">
+        <v>380</v>
+      </c>
+      <c r="C48" s="11">
+        <v>70</v>
+      </c>
+      <c r="D48" s="11">
+        <v>140</v>
+      </c>
+      <c r="E48" s="11">
+        <v>100</v>
+      </c>
+      <c r="F48" s="11">
+        <v>0</v>
+      </c>
+      <c r="G48" s="11">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11">
+        <v>185</v>
+      </c>
+      <c r="I48" s="6">
+        <f t="shared" si="2"/>
+        <v>875</v>
+      </c>
+      <c r="J48" s="6">
+        <f t="shared" si="3"/>
+        <v>565</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N48" s="14" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
@@ -2785,9 +2817,9 @@
       <c r="G49" s="18"/>
       <c r="H49" s="18"/>
       <c r="I49" s="6"/>
-      <c r="K49" s="18"/>
-      <c r="L49" s="18"/>
-      <c r="M49" s="18"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
       <c r="N49" s="19"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -2801,9 +2833,9 @@
       <c r="F50" s="18"/>
       <c r="G50" s="18"/>
       <c r="H50" s="18"/>
-      <c r="K50" s="18"/>
-      <c r="L50" s="18"/>
-      <c r="M50" s="18"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
       <c r="N50" s="19"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -2817,20 +2849,20 @@
       <c r="F51" s="18"/>
       <c r="G51" s="18"/>
       <c r="H51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="18"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
       <c r="N51" s="19"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K47" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K51" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L47" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L51" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M47" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M51" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D070A4E-6B7C-4AB0-BD37-2EA2E882CA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2803D5F-9585-4BAC-B69D-552EE556EEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="74">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -255,6 +255,9 @@
   </si>
   <si>
     <t>REVISION DAY</t>
+  </si>
+  <si>
+    <t>FOCUSED ON ANALYTICAL SKILLS</t>
   </si>
 </sst>
 </file>
@@ -899,7 +902,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I48" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I49" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -995,7 +998,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J48" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J49" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2809,18 +2812,47 @@
       <c r="A49" s="10">
         <v>46295</v>
       </c>
-      <c r="B49" s="18"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-      <c r="H49" s="18"/>
-      <c r="I49" s="6"/>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="19"/>
+      <c r="B49" s="11">
+        <v>400</v>
+      </c>
+      <c r="C49" s="11">
+        <v>80</v>
+      </c>
+      <c r="D49" s="11">
+        <v>135</v>
+      </c>
+      <c r="E49" s="11">
+        <v>120</v>
+      </c>
+      <c r="F49" s="11">
+        <v>0</v>
+      </c>
+      <c r="G49" s="11">
+        <v>0</v>
+      </c>
+      <c r="H49" s="11">
+        <v>190</v>
+      </c>
+      <c r="I49" s="6">
+        <f t="shared" si="2"/>
+        <v>925</v>
+      </c>
+      <c r="J49" s="6">
+        <f t="shared" si="3"/>
+        <v>515</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N49" s="14" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2803D5F-9585-4BAC-B69D-552EE556EEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4207188-4237-44C7-A5EC-96D17E6A14B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="75">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>FOCUSED ON ANALYTICAL SKILLS</t>
+  </si>
+  <si>
+    <t>TOOK SOME REST</t>
   </si>
 </sst>
 </file>
@@ -902,7 +905,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I49" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I50" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -998,7 +1001,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J49" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J50" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2858,17 +2861,47 @@
       <c r="A50" s="10">
         <v>46296</v>
       </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="18"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="19"/>
+      <c r="B50" s="11">
+        <v>420</v>
+      </c>
+      <c r="C50" s="11">
+        <v>55</v>
+      </c>
+      <c r="D50" s="11">
+        <v>130</v>
+      </c>
+      <c r="E50" s="11">
+        <v>95</v>
+      </c>
+      <c r="F50" s="11">
+        <v>0</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11">
+        <v>180</v>
+      </c>
+      <c r="I50" s="6">
+        <f t="shared" si="2"/>
+        <v>880</v>
+      </c>
+      <c r="J50" s="6">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4207188-4237-44C7-A5EC-96D17E6A14B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED3AF76-45E4-4416-AAAD-037BC3C3CD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="76">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>TOOK SOME REST</t>
+  </si>
+  <si>
+    <t>FAMILY GET TOGETHER</t>
   </si>
 </sst>
 </file>
@@ -326,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -374,10 +377,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -905,7 +904,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I50" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I51" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1001,7 +1000,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J50" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J51" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2907,17 +2906,47 @@
       <c r="A51" s="10">
         <v>46297</v>
       </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="18"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="19"/>
+      <c r="B51" s="11">
+        <v>350</v>
+      </c>
+      <c r="C51" s="11">
+        <v>80</v>
+      </c>
+      <c r="D51" s="11">
+        <v>140</v>
+      </c>
+      <c r="E51" s="11">
+        <v>125</v>
+      </c>
+      <c r="F51" s="11">
+        <v>0</v>
+      </c>
+      <c r="G51" s="11">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11">
+        <v>200</v>
+      </c>
+      <c r="I51" s="6">
+        <f t="shared" si="2"/>
+        <v>895</v>
+      </c>
+      <c r="J51" s="6">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N51" s="14" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED3AF76-45E4-4416-AAAD-037BC3C3CD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C496366-9D14-4EB0-B7DF-C2C7368F2CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="76">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -329,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -377,6 +377,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
@@ -904,7 +907,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I51" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I52" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1000,7 +1003,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J51" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J52" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -2948,15 +2951,625 @@
         <v>75</v>
       </c>
     </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="10">
+        <v>46298</v>
+      </c>
+      <c r="B52" s="11">
+        <v>390</v>
+      </c>
+      <c r="C52" s="11">
+        <v>70</v>
+      </c>
+      <c r="D52" s="11">
+        <v>200</v>
+      </c>
+      <c r="E52" s="11">
+        <v>110</v>
+      </c>
+      <c r="F52" s="11">
+        <v>0</v>
+      </c>
+      <c r="G52" s="11">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11">
+        <v>190</v>
+      </c>
+      <c r="I52" s="6">
+        <f t="shared" si="2"/>
+        <v>960</v>
+      </c>
+      <c r="J52" s="6">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N52" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="10">
+        <v>46299</v>
+      </c>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="14"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="10">
+        <v>46300</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="14"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="10">
+        <v>46301</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="14"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="10">
+        <v>46302</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="14"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="10">
+        <v>46303</v>
+      </c>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="14"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="10">
+        <v>46304</v>
+      </c>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="14"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="10">
+        <v>46305</v>
+      </c>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="14"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="10">
+        <v>46306</v>
+      </c>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="14"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="10">
+        <v>46307</v>
+      </c>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="14"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="10">
+        <v>46308</v>
+      </c>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="14"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="10">
+        <v>46309</v>
+      </c>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="11"/>
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+      <c r="N63" s="14"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="10">
+        <v>46310</v>
+      </c>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="14"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="10">
+        <v>46311</v>
+      </c>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="14"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="10">
+        <v>46312</v>
+      </c>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="14"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="10">
+        <v>46313</v>
+      </c>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="14"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="10">
+        <v>46314</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="11"/>
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+      <c r="N68" s="14"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="10">
+        <v>46315</v>
+      </c>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+      <c r="N69" s="14"/>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="10">
+        <v>46316</v>
+      </c>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="14"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="10">
+        <v>46317</v>
+      </c>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+      <c r="N71" s="14"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="10">
+        <v>46318</v>
+      </c>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+      <c r="N72" s="14"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="10">
+        <v>46319</v>
+      </c>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+      <c r="N73" s="14"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A74" s="10">
+        <v>46320</v>
+      </c>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+      <c r="N74" s="14"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="10">
+        <v>46321</v>
+      </c>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="14"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="10">
+        <v>46322</v>
+      </c>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="14"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="10">
+        <v>46323</v>
+      </c>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+      <c r="N77" s="14"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="10">
+        <v>46324</v>
+      </c>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+      <c r="N78" s="14"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="10">
+        <v>46325</v>
+      </c>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+      <c r="N79" s="14"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A80" s="10">
+        <v>46326</v>
+      </c>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+      <c r="N80" s="14"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="18"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="18"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="18"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="18"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="18"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="18"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="18"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="18"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="18"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="18"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="18"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="18"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="18"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" s="18"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="18"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="18"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="18"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="18"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="18"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="18"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K51" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5:K80" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"EXCELLENT,GOOD,NEUTRAL,LOW,STRESSED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L51" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L80" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"VERY SATISFIED,SATISFIED,NEUTRAL,UNSATISFIED,VERY UNSATISFIED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M51" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5:M80" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C496366-9D14-4EB0-B7DF-C2C7368F2CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E73D3EF-923E-46EB-81BC-5F759395AE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="77">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>FAMILY GET TOGETHER</t>
+  </si>
+  <si>
+    <t>ENJOYED WEEKEND</t>
   </si>
 </sst>
 </file>
@@ -378,7 +381,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -907,7 +910,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I52" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I53" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1003,7 +1006,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J52" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J53" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3001,19 +3004,47 @@
       <c r="A53" s="10">
         <v>46299</v>
       </c>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="14"/>
+      <c r="B53" s="11">
+        <v>450</v>
+      </c>
+      <c r="C53" s="11">
+        <v>65</v>
+      </c>
+      <c r="D53" s="11">
+        <v>190</v>
+      </c>
+      <c r="E53" s="11">
+        <v>100</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0</v>
+      </c>
+      <c r="G53" s="11">
+        <v>0</v>
+      </c>
+      <c r="H53" s="11">
+        <v>190</v>
+      </c>
+      <c r="I53" s="6">
+        <f t="shared" si="2"/>
+        <v>995</v>
+      </c>
+      <c r="J53" s="6">
+        <f t="shared" si="3"/>
+        <v>445</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N53" s="14" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E73D3EF-923E-46EB-81BC-5F759395AE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C5733A-46E9-443C-94AC-A1E2C0AC5B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="78">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>ENJOYED WEEKEND</t>
+  </si>
+  <si>
+    <t>ATTENDED ONLINE CLASSES</t>
   </si>
 </sst>
 </file>
@@ -910,7 +913,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I53" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I54" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1006,7 +1009,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J53" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J54" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3050,19 +3053,47 @@
       <c r="A54" s="10">
         <v>46300</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="14"/>
+      <c r="B54" s="11">
+        <v>400</v>
+      </c>
+      <c r="C54" s="11">
+        <v>60</v>
+      </c>
+      <c r="D54" s="11">
+        <v>185</v>
+      </c>
+      <c r="E54" s="11">
+        <v>90</v>
+      </c>
+      <c r="F54" s="11">
+        <v>0</v>
+      </c>
+      <c r="G54" s="11">
+        <v>0</v>
+      </c>
+      <c r="H54" s="11">
+        <v>200</v>
+      </c>
+      <c r="I54" s="6">
+        <f t="shared" si="2"/>
+        <v>935</v>
+      </c>
+      <c r="J54" s="6">
+        <f t="shared" si="3"/>
+        <v>505</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N54" s="14" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C5733A-46E9-443C-94AC-A1E2C0AC5B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A390FAB7-D8F7-486E-8DFF-D2FCE4B46FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="79">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>ATTENDED ONLINE CLASSES</t>
+  </si>
+  <si>
+    <t>PRACTICE DAY</t>
   </si>
 </sst>
 </file>
@@ -913,7 +916,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I54" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I55" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1009,7 +1012,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J54" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J55" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3066,21 +3069,21 @@
         <v>90</v>
       </c>
       <c r="F54" s="11">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G54" s="11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" s="11">
         <v>200</v>
       </c>
       <c r="I54" s="6">
         <f t="shared" si="2"/>
-        <v>935</v>
+        <v>1135</v>
       </c>
       <c r="J54" s="6">
         <f t="shared" si="3"/>
-        <v>505</v>
+        <v>305</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>5</v>
@@ -3099,19 +3102,47 @@
       <c r="A55" s="10">
         <v>46301</v>
       </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="14"/>
+      <c r="B55" s="11">
+        <v>300</v>
+      </c>
+      <c r="C55" s="11">
+        <v>70</v>
+      </c>
+      <c r="D55" s="11">
+        <v>130</v>
+      </c>
+      <c r="E55" s="11">
+        <v>90</v>
+      </c>
+      <c r="F55" s="11">
+        <v>300</v>
+      </c>
+      <c r="G55" s="11">
+        <v>5</v>
+      </c>
+      <c r="H55" s="11">
+        <v>180</v>
+      </c>
+      <c r="I55" s="6">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J55" s="6">
+        <f t="shared" si="3"/>
+        <v>370</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N55" s="14" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A390FAB7-D8F7-486E-8DFF-D2FCE4B46FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E3E66D-71D7-4D40-BCA9-5F4C90B3B1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="80">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>PRACTICE DAY</t>
+  </si>
+  <si>
+    <t>FOLLOWED NORMAL ROUTINE</t>
   </si>
 </sst>
 </file>
@@ -916,7 +919,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I55" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I56" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1012,7 +1015,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J55" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J56" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3148,19 +3151,47 @@
       <c r="A56" s="10">
         <v>46302</v>
       </c>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="14"/>
+      <c r="B56" s="11">
+        <v>480</v>
+      </c>
+      <c r="C56" s="11">
+        <v>70</v>
+      </c>
+      <c r="D56" s="11">
+        <v>150</v>
+      </c>
+      <c r="E56" s="11">
+        <v>85</v>
+      </c>
+      <c r="F56" s="11">
+        <v>300</v>
+      </c>
+      <c r="G56" s="11">
+        <v>5</v>
+      </c>
+      <c r="H56" s="11">
+        <v>170</v>
+      </c>
+      <c r="I56" s="6">
+        <f t="shared" si="2"/>
+        <v>1255</v>
+      </c>
+      <c r="J56" s="6">
+        <f t="shared" si="3"/>
+        <v>185</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N56" s="14" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E3E66D-71D7-4D40-BCA9-5F4C90B3B1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650E8363-231E-45D6-BFE8-CC0C0D3E8892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>FOLLOWED NORMAL ROUTINE</t>
+  </si>
+  <si>
+    <t>OUTING WITH COUSINS</t>
   </si>
 </sst>
 </file>
@@ -919,7 +922,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I56" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I57" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1015,7 +1018,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J56" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J57" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3197,19 +3200,47 @@
       <c r="A57" s="10">
         <v>46303</v>
       </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="14"/>
+      <c r="B57" s="11">
+        <v>400</v>
+      </c>
+      <c r="C57" s="11">
+        <v>60</v>
+      </c>
+      <c r="D57" s="11">
+        <v>140</v>
+      </c>
+      <c r="E57" s="11">
+        <v>70</v>
+      </c>
+      <c r="F57" s="11">
+        <v>0</v>
+      </c>
+      <c r="G57" s="11">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11">
+        <v>200</v>
+      </c>
+      <c r="I57" s="6">
+        <f t="shared" si="2"/>
+        <v>870</v>
+      </c>
+      <c r="J57" s="6">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N57" s="14" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650E8363-231E-45D6-BFE8-CC0C0D3E8892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F1270E-7BD0-4B59-AAE1-C9B3C827A6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="82">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>OUTING WITH COUSINS</t>
+  </si>
+  <si>
+    <t>FELT TIRED TODAY</t>
   </si>
 </sst>
 </file>
@@ -922,7 +925,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I57" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I58" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1018,7 +1021,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J57" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J58" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3246,19 +3249,47 @@
       <c r="A58" s="10">
         <v>46304</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="14"/>
+      <c r="B58" s="11">
+        <v>450</v>
+      </c>
+      <c r="C58" s="11">
+        <v>55</v>
+      </c>
+      <c r="D58" s="11">
+        <v>200</v>
+      </c>
+      <c r="E58" s="11">
+        <v>80</v>
+      </c>
+      <c r="F58" s="11">
+        <v>0</v>
+      </c>
+      <c r="G58" s="11">
+        <v>0</v>
+      </c>
+      <c r="H58" s="11">
+        <v>190</v>
+      </c>
+      <c r="I58" s="6">
+        <f t="shared" si="2"/>
+        <v>975</v>
+      </c>
+      <c r="J58" s="6">
+        <f t="shared" si="3"/>
+        <v>465</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N58" s="14" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F1270E-7BD0-4B59-AAE1-C9B3C827A6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D658BA32-E58E-4FE3-8756-F4B1135B7679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="83">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>FELT TIRED TODAY</t>
+  </si>
+  <si>
+    <t>STARTED PREPARATION OF MTE</t>
   </si>
 </sst>
 </file>
@@ -925,7 +928,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I58" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I59" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1021,7 +1024,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J58" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J59" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3295,19 +3298,47 @@
       <c r="A59" s="10">
         <v>46305</v>
       </c>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="14"/>
+      <c r="B59" s="11">
+        <v>400</v>
+      </c>
+      <c r="C59" s="11">
+        <v>60</v>
+      </c>
+      <c r="D59" s="11">
+        <v>250</v>
+      </c>
+      <c r="E59" s="11">
+        <v>80</v>
+      </c>
+      <c r="F59" s="11">
+        <v>0</v>
+      </c>
+      <c r="G59" s="11">
+        <v>0</v>
+      </c>
+      <c r="H59" s="11">
+        <v>200</v>
+      </c>
+      <c r="I59" s="6">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J59" s="6">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N59" s="14" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D658BA32-E58E-4FE3-8756-F4B1135B7679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD94EB1-C35A-4BE1-9BE3-A67E8AE4D202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="84">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>STARTED PREPARATION OF MTE</t>
+  </si>
+  <si>
+    <t>PREPARED FOR NETWORKING MTE</t>
   </si>
 </sst>
 </file>
@@ -928,7 +931,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I59" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I60" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1024,7 +1027,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J59" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J60" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3344,19 +3347,47 @@
       <c r="A60" s="10">
         <v>46306</v>
       </c>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="14"/>
+      <c r="B60" s="11">
+        <v>380</v>
+      </c>
+      <c r="C60" s="11">
+        <v>50</v>
+      </c>
+      <c r="D60" s="11">
+        <v>350</v>
+      </c>
+      <c r="E60" s="11">
+        <v>90</v>
+      </c>
+      <c r="F60" s="11">
+        <v>0</v>
+      </c>
+      <c r="G60" s="11">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11">
+        <v>180</v>
+      </c>
+      <c r="I60" s="6">
+        <f t="shared" si="2"/>
+        <v>1050</v>
+      </c>
+      <c r="J60" s="6">
+        <f t="shared" si="3"/>
+        <v>390</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N60" s="14" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD94EB1-C35A-4BE1-9BE3-A67E8AE4D202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F532CD0-9E8D-40A7-A87F-0E65733A1DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="85">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>PREPARED FOR NETWORKING MTE</t>
+  </si>
+  <si>
+    <t>PREPARED FOR CPP MTE</t>
   </si>
 </sst>
 </file>
@@ -931,7 +934,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I60" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I61" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1027,7 +1030,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J60" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J61" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3393,19 +3396,47 @@
       <c r="A61" s="10">
         <v>46307</v>
       </c>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="14"/>
+      <c r="B61" s="11">
+        <v>420</v>
+      </c>
+      <c r="C61" s="11">
+        <v>60</v>
+      </c>
+      <c r="D61" s="11">
+        <v>400</v>
+      </c>
+      <c r="E61" s="11">
+        <v>120</v>
+      </c>
+      <c r="F61" s="11">
+        <v>1</v>
+      </c>
+      <c r="G61" s="11">
+        <v>90</v>
+      </c>
+      <c r="H61" s="11">
+        <v>170</v>
+      </c>
+      <c r="I61" s="6">
+        <f t="shared" si="2"/>
+        <v>1171</v>
+      </c>
+      <c r="J61" s="6">
+        <f t="shared" si="3"/>
+        <v>269</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N61" s="14" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F532CD0-9E8D-40A7-A87F-0E65733A1DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C723CF38-4559-4288-9F60-5443CE8DA9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="86">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>PREPARED FOR CPP MTE</t>
+  </si>
+  <si>
+    <t>PREPARED FOR DB MTE</t>
   </si>
 </sst>
 </file>
@@ -934,7 +937,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I61" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I62" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1030,7 +1033,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J61" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J62" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3442,19 +3445,47 @@
       <c r="A62" s="10">
         <v>46308</v>
       </c>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="14"/>
+      <c r="B62" s="11">
+        <v>360</v>
+      </c>
+      <c r="C62" s="11">
+        <v>55</v>
+      </c>
+      <c r="D62" s="11">
+        <v>420</v>
+      </c>
+      <c r="E62" s="11">
+        <v>80</v>
+      </c>
+      <c r="F62" s="11">
+        <v>1</v>
+      </c>
+      <c r="G62" s="11">
+        <v>90</v>
+      </c>
+      <c r="H62" s="11">
+        <v>180</v>
+      </c>
+      <c r="I62" s="6">
+        <f t="shared" si="2"/>
+        <v>1096</v>
+      </c>
+      <c r="J62" s="6">
+        <f t="shared" si="3"/>
+        <v>344</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N62" s="14" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C723CF38-4559-4288-9F60-5443CE8DA9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C085D9-E7A4-4FEE-8F76-924D49FA8043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="87">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>PREPARED FOR DB MTE</t>
+  </si>
+  <si>
+    <t>EXAM WENT WELL</t>
   </si>
 </sst>
 </file>
@@ -937,7 +940,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I62" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I63" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1033,7 +1036,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J62" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J63" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3491,19 +3494,47 @@
       <c r="A63" s="10">
         <v>46309</v>
       </c>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="14"/>
+      <c r="B63" s="11">
+        <v>320</v>
+      </c>
+      <c r="C63" s="11">
+        <v>65</v>
+      </c>
+      <c r="D63" s="11">
+        <v>300</v>
+      </c>
+      <c r="E63" s="11">
+        <v>100</v>
+      </c>
+      <c r="F63" s="11">
+        <v>1</v>
+      </c>
+      <c r="G63" s="11">
+        <v>90</v>
+      </c>
+      <c r="H63" s="11">
+        <v>175</v>
+      </c>
+      <c r="I63" s="6">
+        <f t="shared" si="2"/>
+        <v>961</v>
+      </c>
+      <c r="J63" s="6">
+        <f t="shared" si="3"/>
+        <v>479</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N63" s="14" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C085D9-E7A4-4FEE-8F76-924D49FA8043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D113C366-5F2B-45A4-A7D8-7A1E7E25625A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="88">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>EXAM WENT WELL</t>
+  </si>
+  <si>
+    <t>PREPARED FOR ANALTICAL SKILLS</t>
   </si>
 </sst>
 </file>
@@ -940,7 +943,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I63" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I64" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1036,7 +1039,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J63" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J64" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3540,19 +3543,47 @@
       <c r="A64" s="10">
         <v>46310</v>
       </c>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="14"/>
+      <c r="B64" s="11">
+        <v>480</v>
+      </c>
+      <c r="C64" s="11">
+        <v>70</v>
+      </c>
+      <c r="D64" s="11">
+        <v>450</v>
+      </c>
+      <c r="E64" s="11">
+        <v>70</v>
+      </c>
+      <c r="F64" s="11">
+        <v>0</v>
+      </c>
+      <c r="G64" s="11">
+        <v>0</v>
+      </c>
+      <c r="H64" s="11">
+        <v>190</v>
+      </c>
+      <c r="I64" s="6">
+        <f t="shared" si="2"/>
+        <v>1260</v>
+      </c>
+      <c r="J64" s="6">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N64" s="14" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D113C366-5F2B-45A4-A7D8-7A1E7E25625A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CE6FA9-8724-449C-98B2-EB7E24802037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="89">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>PREPARED FOR ANALTICAL SKILLS</t>
+  </si>
+  <si>
+    <t>PREPARED FOR COMM. MTE</t>
   </si>
 </sst>
 </file>
@@ -943,7 +946,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I64" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I65" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1039,7 +1042,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J64" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J65" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3589,19 +3592,47 @@
       <c r="A65" s="10">
         <v>46311</v>
       </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="14"/>
+      <c r="B65" s="11">
+        <v>300</v>
+      </c>
+      <c r="C65" s="11">
+        <v>65</v>
+      </c>
+      <c r="D65" s="11">
+        <v>420</v>
+      </c>
+      <c r="E65" s="11">
+        <v>70</v>
+      </c>
+      <c r="F65" s="11">
+        <v>1</v>
+      </c>
+      <c r="G65" s="11">
+        <v>90</v>
+      </c>
+      <c r="H65" s="11">
+        <v>180</v>
+      </c>
+      <c r="I65" s="6">
+        <f t="shared" si="2"/>
+        <v>1036</v>
+      </c>
+      <c r="J65" s="6">
+        <f t="shared" si="3"/>
+        <v>404</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N65" s="14" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CE6FA9-8724-449C-98B2-EB7E24802037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB50F0F7-F362-44BC-988C-6A9CBBC2AA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="90">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>PREPARED FOR COMM. MTE</t>
+  </si>
+  <si>
+    <t>MTE FINISHED</t>
   </si>
 </sst>
 </file>
@@ -946,7 +949,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I65" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I66" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1042,7 +1045,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J65" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J66" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3638,19 +3641,47 @@
       <c r="A66" s="10">
         <v>46312</v>
       </c>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="14"/>
+      <c r="B66" s="11">
+        <v>400</v>
+      </c>
+      <c r="C66" s="11">
+        <v>65</v>
+      </c>
+      <c r="D66" s="11">
+        <v>300</v>
+      </c>
+      <c r="E66" s="11">
+        <v>80</v>
+      </c>
+      <c r="F66" s="11">
+        <v>1</v>
+      </c>
+      <c r="G66" s="11">
+        <v>90</v>
+      </c>
+      <c r="H66" s="11">
+        <v>190</v>
+      </c>
+      <c r="I66" s="6">
+        <f t="shared" si="2"/>
+        <v>1036</v>
+      </c>
+      <c r="J66" s="6">
+        <f t="shared" si="3"/>
+        <v>404</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N66" s="14" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB50F0F7-F362-44BC-988C-6A9CBBC2AA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFFCDB2-5F60-4493-8CF9-04A8A5177558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="91">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>MTE FINISHED</t>
+  </si>
+  <si>
+    <t>TAKEN A REST DAY</t>
   </si>
 </sst>
 </file>
@@ -949,7 +952,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I66" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I67" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1045,7 +1048,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J66" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J67" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3687,19 +3690,47 @@
       <c r="A67" s="10">
         <v>46313</v>
       </c>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="14"/>
+      <c r="B67" s="11">
+        <v>450</v>
+      </c>
+      <c r="C67" s="11">
+        <v>70</v>
+      </c>
+      <c r="D67" s="11">
+        <v>250</v>
+      </c>
+      <c r="E67" s="11">
+        <v>100</v>
+      </c>
+      <c r="F67" s="11">
+        <v>0</v>
+      </c>
+      <c r="G67" s="11">
+        <v>0</v>
+      </c>
+      <c r="H67" s="11">
+        <v>200</v>
+      </c>
+      <c r="I67" s="6">
+        <f t="shared" si="2"/>
+        <v>1070</v>
+      </c>
+      <c r="J67" s="6">
+        <f t="shared" si="3"/>
+        <v>370</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N67" s="14" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFFCDB2-5F60-4493-8CF9-04A8A5177558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED409B84-1D2A-4BD0-9D29-2318EBD5A9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>TAKEN A REST DAY</t>
+  </si>
+  <si>
+    <t>RESUME NORMAL CLASSES</t>
   </si>
 </sst>
 </file>
@@ -952,7 +955,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I67" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I68" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1048,7 +1051,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J67" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J68" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3427,21 +3430,21 @@
         <v>120</v>
       </c>
       <c r="F61" s="11">
+        <v>90</v>
+      </c>
+      <c r="G61" s="11">
         <v>1</v>
-      </c>
-      <c r="G61" s="11">
-        <v>90</v>
       </c>
       <c r="H61" s="11">
         <v>170</v>
       </c>
       <c r="I61" s="6">
         <f t="shared" si="2"/>
-        <v>1171</v>
+        <v>1260</v>
       </c>
       <c r="J61" s="6">
         <f t="shared" si="3"/>
-        <v>269</v>
+        <v>180</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>5</v>
@@ -3473,21 +3476,21 @@
         <v>80</v>
       </c>
       <c r="F62" s="11">
+        <v>90</v>
+      </c>
+      <c r="G62" s="11">
         <v>1</v>
-      </c>
-      <c r="G62" s="11">
-        <v>90</v>
       </c>
       <c r="H62" s="11">
         <v>180</v>
       </c>
       <c r="I62" s="6">
         <f t="shared" si="2"/>
-        <v>1096</v>
+        <v>1185</v>
       </c>
       <c r="J62" s="6">
         <f t="shared" si="3"/>
-        <v>344</v>
+        <v>255</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>6</v>
@@ -3519,21 +3522,21 @@
         <v>100</v>
       </c>
       <c r="F63" s="11">
+        <v>90</v>
+      </c>
+      <c r="G63" s="11">
         <v>1</v>
-      </c>
-      <c r="G63" s="11">
-        <v>90</v>
       </c>
       <c r="H63" s="11">
         <v>175</v>
       </c>
       <c r="I63" s="6">
         <f t="shared" si="2"/>
-        <v>961</v>
+        <v>1050</v>
       </c>
       <c r="J63" s="6">
         <f t="shared" si="3"/>
-        <v>479</v>
+        <v>390</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>5</v>
@@ -3611,21 +3614,21 @@
         <v>70</v>
       </c>
       <c r="F65" s="11">
+        <v>90</v>
+      </c>
+      <c r="G65" s="11">
         <v>1</v>
-      </c>
-      <c r="G65" s="11">
-        <v>90</v>
       </c>
       <c r="H65" s="11">
         <v>180</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="2"/>
-        <v>1036</v>
+        <v>1125</v>
       </c>
       <c r="J65" s="6">
         <f t="shared" si="3"/>
-        <v>404</v>
+        <v>315</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>6</v>
@@ -3657,21 +3660,21 @@
         <v>80</v>
       </c>
       <c r="F66" s="11">
+        <v>90</v>
+      </c>
+      <c r="G66" s="11">
         <v>1</v>
-      </c>
-      <c r="G66" s="11">
-        <v>90</v>
       </c>
       <c r="H66" s="11">
         <v>190</v>
       </c>
       <c r="I66" s="6">
         <f t="shared" si="2"/>
-        <v>1036</v>
+        <v>1125</v>
       </c>
       <c r="J66" s="6">
         <f t="shared" si="3"/>
-        <v>404</v>
+        <v>315</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>9</v>
@@ -3736,19 +3739,47 @@
       <c r="A68" s="10">
         <v>46314</v>
       </c>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="14"/>
+      <c r="B68" s="11">
+        <v>300</v>
+      </c>
+      <c r="C68" s="11">
+        <v>60</v>
+      </c>
+      <c r="D68" s="11">
+        <v>190</v>
+      </c>
+      <c r="E68" s="11">
+        <v>90</v>
+      </c>
+      <c r="F68" s="11">
+        <v>200</v>
+      </c>
+      <c r="G68" s="11">
+        <v>4</v>
+      </c>
+      <c r="H68" s="11">
+        <v>190</v>
+      </c>
+      <c r="I68" s="6">
+        <f t="shared" si="2"/>
+        <v>1030</v>
+      </c>
+      <c r="J68" s="6">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N68" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED409B84-1D2A-4BD0-9D29-2318EBD5A9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B31958-6A0E-41D7-94A6-872991324BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="93">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>RESUME NORMAL CLASSES</t>
+  </si>
+  <si>
+    <t>ENJOYED DUSSEHRA</t>
   </si>
 </sst>
 </file>
@@ -955,7 +958,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I68" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I69" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1051,7 +1054,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J68" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J69" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3785,19 +3788,47 @@
       <c r="A69" s="10">
         <v>46315</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="14"/>
+      <c r="B69" s="11">
+        <v>350</v>
+      </c>
+      <c r="C69" s="11">
+        <v>65</v>
+      </c>
+      <c r="D69" s="11">
+        <v>190</v>
+      </c>
+      <c r="E69" s="11">
+        <v>100</v>
+      </c>
+      <c r="F69" s="11">
+        <v>0</v>
+      </c>
+      <c r="G69" s="11">
+        <v>0</v>
+      </c>
+      <c r="H69" s="11">
+        <v>200</v>
+      </c>
+      <c r="I69" s="6">
+        <f t="shared" si="2"/>
+        <v>905</v>
+      </c>
+      <c r="J69" s="6">
+        <f t="shared" si="3"/>
+        <v>535</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N69" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B31958-6A0E-41D7-94A6-872991324BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB15019-91F4-4362-88DC-AD5AF1B2FFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="94">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>ENJOYED DUSSEHRA</t>
+  </si>
+  <si>
+    <t>ATTENDED FAMILY FUNCTION</t>
   </si>
 </sst>
 </file>
@@ -958,7 +961,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I69" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I70" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1054,7 +1057,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J69" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J70" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3834,19 +3837,47 @@
       <c r="A70" s="10">
         <v>46316</v>
       </c>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="11"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="14"/>
+      <c r="B70" s="11">
+        <v>480</v>
+      </c>
+      <c r="C70" s="11">
+        <v>70</v>
+      </c>
+      <c r="D70" s="11">
+        <v>150</v>
+      </c>
+      <c r="E70" s="11">
+        <v>100</v>
+      </c>
+      <c r="F70" s="11">
+        <v>0</v>
+      </c>
+      <c r="G70" s="11">
+        <v>0</v>
+      </c>
+      <c r="H70" s="11">
+        <v>190</v>
+      </c>
+      <c r="I70" s="6">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J70" s="6">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N70" s="14" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB15019-91F4-4362-88DC-AD5AF1B2FFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F381E92-AFEB-47E4-B60E-F63E0CFD4A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="95">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>ATTENDED FAMILY FUNCTION</t>
+  </si>
+  <si>
+    <t>REGULAR DAY</t>
   </si>
 </sst>
 </file>
@@ -961,7 +964,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I70" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I71" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1057,7 +1060,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J70" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J71" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3883,19 +3886,47 @@
       <c r="A71" s="10">
         <v>46317</v>
       </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="14"/>
+      <c r="B71" s="11">
+        <v>250</v>
+      </c>
+      <c r="C71" s="11">
+        <v>75</v>
+      </c>
+      <c r="D71" s="11">
+        <v>170</v>
+      </c>
+      <c r="E71" s="11">
+        <v>110</v>
+      </c>
+      <c r="F71" s="11">
+        <v>360</v>
+      </c>
+      <c r="G71" s="11">
+        <v>6</v>
+      </c>
+      <c r="H71" s="11">
+        <v>170</v>
+      </c>
+      <c r="I71" s="6">
+        <f t="shared" si="2"/>
+        <v>1135</v>
+      </c>
+      <c r="J71" s="6">
+        <f t="shared" si="3"/>
+        <v>305</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N71" s="14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F381E92-AFEB-47E4-B60E-F63E0CFD4A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2230A42-234A-42A4-A796-B48AE72F8929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="95">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -964,7 +964,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I71" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I72" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1060,7 +1060,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J71" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J72" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3932,19 +3932,47 @@
       <c r="A72" s="10">
         <v>46318</v>
       </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="14"/>
+      <c r="B72" s="11">
+        <v>350</v>
+      </c>
+      <c r="C72" s="11">
+        <v>65</v>
+      </c>
+      <c r="D72" s="11">
+        <v>140</v>
+      </c>
+      <c r="E72" s="11">
+        <v>90</v>
+      </c>
+      <c r="F72" s="11">
+        <v>420</v>
+      </c>
+      <c r="G72" s="11">
+        <v>7</v>
+      </c>
+      <c r="H72" s="11">
+        <v>160</v>
+      </c>
+      <c r="I72" s="6">
+        <f t="shared" si="2"/>
+        <v>1225</v>
+      </c>
+      <c r="J72" s="6">
+        <f t="shared" si="3"/>
+        <v>215</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N72" s="14" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2230A42-234A-42A4-A796-B48AE72F8929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA91A488-5A93-4344-A864-2DAC15B76F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="95">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -964,7 +964,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I72" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I73" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1060,7 +1060,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J72" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J73" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -3978,19 +3978,47 @@
       <c r="A73" s="10">
         <v>46319</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="14"/>
+      <c r="B73" s="11">
+        <v>390</v>
+      </c>
+      <c r="C73" s="11">
+        <v>70</v>
+      </c>
+      <c r="D73" s="11">
+        <v>150</v>
+      </c>
+      <c r="E73" s="11">
+        <v>80</v>
+      </c>
+      <c r="F73" s="11">
+        <v>50</v>
+      </c>
+      <c r="G73" s="11">
+        <v>1</v>
+      </c>
+      <c r="H73" s="11">
+        <v>190</v>
+      </c>
+      <c r="I73" s="6">
+        <f t="shared" si="2"/>
+        <v>930</v>
+      </c>
+      <c r="J73" s="6">
+        <f t="shared" si="3"/>
+        <v>510</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N73" s="14" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA91A488-5A93-4344-A864-2DAC15B76F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99B7BF2-5299-473A-A40F-10E745F877F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="96">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>REGULAR DAY</t>
+  </si>
+  <si>
+    <t>DID APTITUDE TEST</t>
   </si>
 </sst>
 </file>
@@ -964,7 +967,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I73" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I74" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1060,7 +1063,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J73" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J74" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -4024,19 +4027,47 @@
       <c r="A74" s="10">
         <v>46320</v>
       </c>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="11"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="6"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="14"/>
+      <c r="B74" s="11">
+        <v>480</v>
+      </c>
+      <c r="C74" s="11">
+        <v>60</v>
+      </c>
+      <c r="D74" s="11">
+        <v>190</v>
+      </c>
+      <c r="E74" s="11">
+        <v>105</v>
+      </c>
+      <c r="F74" s="11">
+        <v>0</v>
+      </c>
+      <c r="G74" s="11">
+        <v>0</v>
+      </c>
+      <c r="H74" s="11">
+        <v>200</v>
+      </c>
+      <c r="I74" s="6">
+        <f t="shared" si="2"/>
+        <v>1035</v>
+      </c>
+      <c r="J74" s="6">
+        <f t="shared" si="3"/>
+        <v>405</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N74" s="14" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99B7BF2-5299-473A-A40F-10E745F877F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB610296-8477-426B-95ED-5FA60592A33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="96">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -967,7 +967,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I74" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I75" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1063,7 +1063,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J74" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J75" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -4073,19 +4073,47 @@
       <c r="A75" s="10">
         <v>46321</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="11"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="14"/>
+      <c r="B75" s="11">
+        <v>480</v>
+      </c>
+      <c r="C75" s="11">
+        <v>60</v>
+      </c>
+      <c r="D75" s="11">
+        <v>180</v>
+      </c>
+      <c r="E75" s="11">
+        <v>100</v>
+      </c>
+      <c r="F75" s="11">
+        <v>0</v>
+      </c>
+      <c r="G75" s="11">
+        <v>0</v>
+      </c>
+      <c r="H75" s="11">
+        <v>185</v>
+      </c>
+      <c r="I75" s="6">
+        <f t="shared" si="2"/>
+        <v>1005</v>
+      </c>
+      <c r="J75" s="6">
+        <f t="shared" si="3"/>
+        <v>435</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N75" s="14" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB610296-8477-426B-95ED-5FA60592A33D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522EE6E4-2B15-4D21-AE2B-3521AB8365E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="97">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>DID APTITUDE TEST</t>
+  </si>
+  <si>
+    <t>CELEBRATED GURPURAB</t>
   </si>
 </sst>
 </file>
@@ -967,7 +970,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I75" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I76" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1063,7 +1066,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J75" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J76" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -4119,19 +4122,47 @@
       <c r="A76" s="10">
         <v>46322</v>
       </c>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="6"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="14"/>
+      <c r="B76" s="11">
+        <v>360</v>
+      </c>
+      <c r="C76" s="11">
+        <v>80</v>
+      </c>
+      <c r="D76" s="11">
+        <v>140</v>
+      </c>
+      <c r="E76" s="11">
+        <v>80</v>
+      </c>
+      <c r="F76" s="11">
+        <v>300</v>
+      </c>
+      <c r="G76" s="11">
+        <v>5</v>
+      </c>
+      <c r="H76" s="11">
+        <v>180</v>
+      </c>
+      <c r="I76" s="6">
+        <f t="shared" si="2"/>
+        <v>1140</v>
+      </c>
+      <c r="J76" s="6">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N76" s="14" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{522EE6E4-2B15-4D21-AE2B-3521AB8365E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368CBF6-A3DD-4D8A-AB67-8A58AE36D0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="98">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>CELEBRATED GURPURAB</t>
+  </si>
+  <si>
+    <t>MIXED VIBES</t>
   </si>
 </sst>
 </file>
@@ -970,7 +973,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I76" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I77" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1066,7 +1069,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J76" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J77" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -4168,19 +4171,47 @@
       <c r="A77" s="10">
         <v>46323</v>
       </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="14"/>
+      <c r="B77" s="11">
+        <v>480</v>
+      </c>
+      <c r="C77" s="11">
+        <v>70</v>
+      </c>
+      <c r="D77" s="11">
+        <v>160</v>
+      </c>
+      <c r="E77" s="11">
+        <v>90</v>
+      </c>
+      <c r="F77" s="11">
+        <v>300</v>
+      </c>
+      <c r="G77" s="11">
+        <v>5</v>
+      </c>
+      <c r="H77" s="11">
+        <v>150</v>
+      </c>
+      <c r="I77" s="6">
+        <f t="shared" si="2"/>
+        <v>1250</v>
+      </c>
+      <c r="J77" s="6">
+        <f t="shared" si="3"/>
+        <v>190</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N77" s="14" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368CBF6-A3DD-4D8A-AB67-8A58AE36D0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0274F48E-EAA8-4327-ADA5-6C0AFBAAF093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="98">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -973,7 +973,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I77" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I78" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1069,7 +1069,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J77" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J78" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -4217,19 +4217,47 @@
       <c r="A78" s="10">
         <v>46324</v>
       </c>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="14"/>
+      <c r="B78" s="11">
+        <v>420</v>
+      </c>
+      <c r="C78" s="11">
+        <v>60</v>
+      </c>
+      <c r="D78" s="11">
+        <v>155</v>
+      </c>
+      <c r="E78" s="11">
+        <v>80</v>
+      </c>
+      <c r="F78" s="11">
+        <v>300</v>
+      </c>
+      <c r="G78" s="11">
+        <v>5</v>
+      </c>
+      <c r="H78" s="11">
+        <v>165</v>
+      </c>
+      <c r="I78" s="6">
+        <f t="shared" si="2"/>
+        <v>1180</v>
+      </c>
+      <c r="J78" s="6">
+        <f t="shared" si="3"/>
+        <v>260</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N78" s="14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="10">

--- a/12613027.xlsx
+++ b/12613027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krama\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0274F48E-EAA8-4327-ADA5-6C0AFBAAF093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2E2462-B855-4601-B966-B3CE65703D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="99">
   <si>
     <t>CLASSES ATTENDED</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>MIXED VIBES</t>
+  </si>
+  <si>
+    <t>LOW DAY</t>
   </si>
 </sst>
 </file>
@@ -973,7 +976,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I78" si="2">SUM(B7:F7,H7)</f>
+        <f t="shared" ref="I7:I79" si="2">SUM(B7:F7,H7)</f>
         <v>1090</v>
       </c>
       <c r="J7" s="5">
@@ -1069,7 +1072,7 @@
         <v>1115</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" ref="J9:J78" si="3">1440-I9</f>
+        <f t="shared" ref="J9:J79" si="3">1440-I9</f>
         <v>325</v>
       </c>
       <c r="K9" s="11" t="s">
@@ -4263,19 +4266,47 @@
       <c r="A79" s="10">
         <v>46325</v>
       </c>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="14"/>
+      <c r="B79" s="11">
+        <v>450</v>
+      </c>
+      <c r="C79" s="11">
+        <v>60</v>
+      </c>
+      <c r="D79" s="11">
+        <v>130</v>
+      </c>
+      <c r="E79" s="11">
+        <v>90</v>
+      </c>
+      <c r="F79" s="11">
+        <v>420</v>
+      </c>
+      <c r="G79" s="11">
+        <v>7</v>
+      </c>
+      <c r="H79" s="11">
+        <v>180</v>
+      </c>
+      <c r="I79" s="6">
+        <f t="shared" si="2"/>
+        <v>1330</v>
+      </c>
+      <c r="J79" s="6">
+        <f t="shared" si="3"/>
+        <v>110</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="N79" s="14" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
